--- a/data/upload/packing/TJ-25-26-189.xlsx
+++ b/data/upload/packing/TJ-25-26-189.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\TJ_25-26_189 NE_Gregory LB_SB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B3ECD9A-9707-4258-9A32-CD4111B3EE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD5FF5F-8B84-48AE-95B7-42BAE6401A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spool List" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5918" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5918" uniqueCount="1427">
   <si>
     <t>Project Code</t>
   </si>
@@ -4317,6 +4317,9 @@
   </si>
   <si>
     <t>251235_00-LP-008-03</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -4328,7 +4331,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4383,6 +4386,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -4434,7 +4443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -4511,13 +4520,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4565,6 +4585,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5147,7 +5170,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="NavDataRegion" displayName="NavDataRegion" ref="A2:U722" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22">
-  <autoFilter ref="A2:U722" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A2:U722" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="4">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Project Code" dataDxfId="20"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Drawing No." dataDxfId="19"/>
@@ -5451,8 +5480,9 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" customWidth="1"/>
-    <col min="7" max="10" width="20" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="10" width="20" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="15.28515625" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.5703125" customWidth="1"/>
@@ -5472,11 +5502,11 @@
       </c>
       <c r="O1" s="4">
         <f>SUBTOTAL(9,NavDataRegion[Total Qty])</f>
-        <v>728</v>
+        <v>120</v>
       </c>
       <c r="P1" s="15">
         <f>SUBTOTAL(9,NavDataRegion[Total Wt])</f>
-        <v>136076.10540082495</v>
+        <v>47344.691550000018</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -5544,7 +5574,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -5594,7 +5624,7 @@
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
     </row>
-    <row r="4" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -5620,7 +5650,7 @@
         <v>256</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>16</v>
@@ -5644,7 +5674,7 @@
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -5694,7 +5724,7 @@
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -5720,7 +5750,7 @@
         <v>779</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>16</v>
@@ -5744,7 +5774,7 @@
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -5794,7 +5824,7 @@
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -5820,7 +5850,7 @@
         <v>955</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>16</v>
@@ -5844,7 +5874,7 @@
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -5870,7 +5900,7 @@
         <v>1075</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>16</v>
@@ -5894,7 +5924,7 @@
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -5944,7 +5974,7 @@
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -5994,7 +6024,7 @@
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6044,7 +6074,7 @@
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -6094,7 +6124,7 @@
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>11</v>
       </c>
@@ -6144,7 +6174,7 @@
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -6194,7 +6224,7 @@
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
@@ -6244,7 +6274,7 @@
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
@@ -6294,7 +6324,7 @@
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>11</v>
       </c>
@@ -6344,7 +6374,7 @@
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>11</v>
       </c>
@@ -6394,7 +6424,7 @@
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>11</v>
       </c>
@@ -6444,7 +6474,7 @@
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
@@ -6494,7 +6524,7 @@
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>11</v>
       </c>
@@ -6544,7 +6574,7 @@
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
@@ -6594,7 +6624,7 @@
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>11</v>
       </c>
@@ -6644,7 +6674,7 @@
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
     </row>
-    <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>11</v>
       </c>
@@ -6694,7 +6724,7 @@
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
     </row>
-    <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>11</v>
       </c>
@@ -6744,7 +6774,7 @@
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
     </row>
-    <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>11</v>
       </c>
@@ -6794,7 +6824,7 @@
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
     </row>
-    <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>11</v>
       </c>
@@ -6844,7 +6874,7 @@
       <c r="T28" s="2"/>
       <c r="U28" s="2"/>
     </row>
-    <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>11</v>
       </c>
@@ -6894,7 +6924,7 @@
       <c r="T29" s="2"/>
       <c r="U29" s="2"/>
     </row>
-    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>11</v>
       </c>
@@ -6944,7 +6974,7 @@
       <c r="T30" s="2"/>
       <c r="U30" s="2"/>
     </row>
-    <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
@@ -6994,7 +7024,7 @@
       <c r="T31" s="2"/>
       <c r="U31" s="2"/>
     </row>
-    <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>11</v>
       </c>
@@ -7044,7 +7074,7 @@
       <c r="T32" s="2"/>
       <c r="U32" s="2"/>
     </row>
-    <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -7094,7 +7124,7 @@
       <c r="T33" s="2"/>
       <c r="U33" s="2"/>
     </row>
-    <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>11</v>
       </c>
@@ -7120,7 +7150,7 @@
         <v>325</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>16</v>
@@ -7144,7 +7174,7 @@
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
     </row>
-    <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>11</v>
       </c>
@@ -7194,7 +7224,7 @@
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
     </row>
-    <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>11</v>
       </c>
@@ -7244,7 +7274,7 @@
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
     </row>
-    <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>11</v>
       </c>
@@ -7294,7 +7324,7 @@
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
     </row>
-    <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>11</v>
       </c>
@@ -7344,7 +7374,7 @@
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
     </row>
-    <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
@@ -7394,7 +7424,7 @@
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
     </row>
-    <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>11</v>
       </c>
@@ -7444,7 +7474,7 @@
       <c r="T40" s="2"/>
       <c r="U40" s="2"/>
     </row>
-    <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>11</v>
       </c>
@@ -7494,7 +7524,7 @@
       <c r="T41" s="2"/>
       <c r="U41" s="2"/>
     </row>
-    <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>11</v>
       </c>
@@ -7544,7 +7574,7 @@
       <c r="T42" s="2"/>
       <c r="U42" s="2"/>
     </row>
-    <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>11</v>
       </c>
@@ -7594,7 +7624,7 @@
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
     </row>
-    <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
@@ -7644,7 +7674,7 @@
       <c r="T44" s="2"/>
       <c r="U44" s="2"/>
     </row>
-    <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>11</v>
       </c>
@@ -7694,7 +7724,7 @@
       <c r="T45" s="2"/>
       <c r="U45" s="2"/>
     </row>
-    <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>11</v>
       </c>
@@ -7744,7 +7774,7 @@
       <c r="T46" s="2"/>
       <c r="U46" s="2"/>
     </row>
-    <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>11</v>
       </c>
@@ -7794,7 +7824,7 @@
       <c r="T47" s="2"/>
       <c r="U47" s="2"/>
     </row>
-    <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
@@ -7844,7 +7874,7 @@
       <c r="T48" s="2"/>
       <c r="U48" s="2"/>
     </row>
-    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>11</v>
       </c>
@@ -7894,7 +7924,7 @@
       <c r="T49" s="2"/>
       <c r="U49" s="2"/>
     </row>
-    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -7944,7 +7974,7 @@
       <c r="T50" s="2"/>
       <c r="U50" s="2"/>
     </row>
-    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>11</v>
       </c>
@@ -7994,7 +8024,7 @@
       <c r="T51" s="2"/>
       <c r="U51" s="2"/>
     </row>
-    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>11</v>
       </c>
@@ -8044,7 +8074,7 @@
       <c r="T52" s="2"/>
       <c r="U52" s="2"/>
     </row>
-    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>11</v>
       </c>
@@ -8070,7 +8100,7 @@
         <v>442</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>16</v>
@@ -8094,7 +8124,7 @@
       <c r="T53" s="2"/>
       <c r="U53" s="2"/>
     </row>
-    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>11</v>
       </c>
@@ -8144,7 +8174,7 @@
       <c r="T54" s="2"/>
       <c r="U54" s="2"/>
     </row>
-    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>11</v>
       </c>
@@ -8194,7 +8224,7 @@
       <c r="T55" s="2"/>
       <c r="U55" s="2"/>
     </row>
-    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>11</v>
       </c>
@@ -8244,7 +8274,7 @@
       <c r="T56" s="2"/>
       <c r="U56" s="2"/>
     </row>
-    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>11</v>
       </c>
@@ -8294,7 +8324,7 @@
       <c r="T57" s="2"/>
       <c r="U57" s="2"/>
     </row>
-    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>11</v>
       </c>
@@ -8344,7 +8374,7 @@
       <c r="T58" s="2"/>
       <c r="U58" s="2"/>
     </row>
-    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -8394,7 +8424,7 @@
       <c r="T59" s="2"/>
       <c r="U59" s="2"/>
     </row>
-    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>11</v>
       </c>
@@ -8444,7 +8474,7 @@
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
     </row>
-    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>11</v>
       </c>
@@ -8494,7 +8524,7 @@
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
     </row>
-    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
@@ -8544,7 +8574,7 @@
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
     </row>
-    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
@@ -8594,7 +8624,7 @@
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
     </row>
-    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>11</v>
       </c>
@@ -8644,7 +8674,7 @@
       <c r="T64" s="2"/>
       <c r="U64" s="2"/>
     </row>
-    <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>11</v>
       </c>
@@ -8694,7 +8724,7 @@
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
     </row>
-    <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>11</v>
       </c>
@@ -8744,7 +8774,7 @@
       <c r="T66" s="2"/>
       <c r="U66" s="2"/>
     </row>
-    <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>11</v>
       </c>
@@ -8794,7 +8824,7 @@
       <c r="T67" s="2"/>
       <c r="U67" s="2"/>
     </row>
-    <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>11</v>
       </c>
@@ -8844,7 +8874,7 @@
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
     </row>
-    <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>11</v>
       </c>
@@ -8894,7 +8924,7 @@
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
     </row>
-    <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>11</v>
       </c>
@@ -8944,7 +8974,7 @@
       <c r="T70" s="2"/>
       <c r="U70" s="2"/>
     </row>
-    <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>11</v>
       </c>
@@ -8994,7 +9024,7 @@
       <c r="T71" s="2"/>
       <c r="U71" s="2"/>
     </row>
-    <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>11</v>
       </c>
@@ -9044,7 +9074,7 @@
       <c r="T72" s="2"/>
       <c r="U72" s="2"/>
     </row>
-    <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>11</v>
       </c>
@@ -9094,7 +9124,7 @@
       <c r="T73" s="2"/>
       <c r="U73" s="2"/>
     </row>
-    <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>11</v>
       </c>
@@ -9144,7 +9174,7 @@
       <c r="T74" s="2"/>
       <c r="U74" s="2"/>
     </row>
-    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>11</v>
       </c>
@@ -9194,7 +9224,7 @@
       <c r="T75" s="2"/>
       <c r="U75" s="2"/>
     </row>
-    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>11</v>
       </c>
@@ -9244,7 +9274,7 @@
       <c r="T76" s="2"/>
       <c r="U76" s="2"/>
     </row>
-    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>11</v>
       </c>
@@ -9294,7 +9324,7 @@
       <c r="T77" s="2"/>
       <c r="U77" s="2"/>
     </row>
-    <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>11</v>
       </c>
@@ -9344,7 +9374,7 @@
       <c r="T78" s="2"/>
       <c r="U78" s="2"/>
     </row>
-    <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>11</v>
       </c>
@@ -9394,7 +9424,7 @@
       <c r="T79" s="2"/>
       <c r="U79" s="2"/>
     </row>
-    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>11</v>
       </c>
@@ -9444,7 +9474,7 @@
       <c r="T80" s="2"/>
       <c r="U80" s="2"/>
     </row>
-    <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>11</v>
       </c>
@@ -9494,7 +9524,7 @@
       <c r="T81" s="2"/>
       <c r="U81" s="2"/>
     </row>
-    <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>11</v>
       </c>
@@ -9544,7 +9574,7 @@
       <c r="T82" s="2"/>
       <c r="U82" s="2"/>
     </row>
-    <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>11</v>
       </c>
@@ -9594,7 +9624,7 @@
       <c r="T83" s="2"/>
       <c r="U83" s="2"/>
     </row>
-    <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>11</v>
       </c>
@@ -9644,7 +9674,7 @@
       <c r="T84" s="2"/>
       <c r="U84" s="2"/>
     </row>
-    <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>11</v>
       </c>
@@ -9694,7 +9724,7 @@
       <c r="T85" s="2"/>
       <c r="U85" s="2"/>
     </row>
-    <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>11</v>
       </c>
@@ -9744,7 +9774,7 @@
       <c r="T86" s="2"/>
       <c r="U86" s="2"/>
     </row>
-    <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>11</v>
       </c>
@@ -9794,7 +9824,7 @@
       <c r="T87" s="2"/>
       <c r="U87" s="2"/>
     </row>
-    <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>11</v>
       </c>
@@ -9844,7 +9874,7 @@
       <c r="T88" s="2"/>
       <c r="U88" s="2"/>
     </row>
-    <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>11</v>
       </c>
@@ -9894,7 +9924,7 @@
       <c r="T89" s="2"/>
       <c r="U89" s="2"/>
     </row>
-    <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>11</v>
       </c>
@@ -9944,7 +9974,7 @@
       <c r="T90" s="2"/>
       <c r="U90" s="2"/>
     </row>
-    <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>11</v>
       </c>
@@ -9994,7 +10024,7 @@
       <c r="T91" s="2"/>
       <c r="U91" s="2"/>
     </row>
-    <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>11</v>
       </c>
@@ -10044,7 +10074,7 @@
       <c r="T92" s="2"/>
       <c r="U92" s="2"/>
     </row>
-    <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>11</v>
       </c>
@@ -10094,7 +10124,7 @@
       <c r="T93" s="2"/>
       <c r="U93" s="2"/>
     </row>
-    <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>11</v>
       </c>
@@ -10144,7 +10174,7 @@
       <c r="T94" s="2"/>
       <c r="U94" s="2"/>
     </row>
-    <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>11</v>
       </c>
@@ -10194,7 +10224,7 @@
       <c r="T95" s="2"/>
       <c r="U95" s="2"/>
     </row>
-    <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>11</v>
       </c>
@@ -10244,7 +10274,7 @@
       <c r="T96" s="2"/>
       <c r="U96" s="2"/>
     </row>
-    <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>11</v>
       </c>
@@ -10294,7 +10324,7 @@
       <c r="T97" s="2"/>
       <c r="U97" s="2"/>
     </row>
-    <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>11</v>
       </c>
@@ -10344,7 +10374,7 @@
       <c r="T98" s="2"/>
       <c r="U98" s="2"/>
     </row>
-    <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>11</v>
       </c>
@@ -10394,7 +10424,7 @@
       <c r="T99" s="2"/>
       <c r="U99" s="2"/>
     </row>
-    <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>11</v>
       </c>
@@ -10444,7 +10474,7 @@
       <c r="T100" s="2"/>
       <c r="U100" s="2"/>
     </row>
-    <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>11</v>
       </c>
@@ -10494,7 +10524,7 @@
       <c r="T101" s="2"/>
       <c r="U101" s="2"/>
     </row>
-    <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>11</v>
       </c>
@@ -10544,7 +10574,7 @@
       <c r="T102" s="2"/>
       <c r="U102" s="2"/>
     </row>
-    <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -10594,7 +10624,7 @@
       <c r="T103" s="2"/>
       <c r="U103" s="2"/>
     </row>
-    <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>11</v>
       </c>
@@ -10644,7 +10674,7 @@
       <c r="T104" s="2"/>
       <c r="U104" s="2"/>
     </row>
-    <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>11</v>
       </c>
@@ -10694,7 +10724,7 @@
       <c r="T105" s="2"/>
       <c r="U105" s="2"/>
     </row>
-    <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>11</v>
       </c>
@@ -10744,7 +10774,7 @@
       <c r="T106" s="2"/>
       <c r="U106" s="2"/>
     </row>
-    <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>11</v>
       </c>
@@ -10794,7 +10824,7 @@
       <c r="T107" s="2"/>
       <c r="U107" s="2"/>
     </row>
-    <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>11</v>
       </c>
@@ -10844,7 +10874,7 @@
       <c r="T108" s="2"/>
       <c r="U108" s="2"/>
     </row>
-    <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>11</v>
       </c>
@@ -10894,7 +10924,7 @@
       <c r="T109" s="2"/>
       <c r="U109" s="2"/>
     </row>
-    <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>11</v>
       </c>
@@ -10944,7 +10974,7 @@
       <c r="T110" s="2"/>
       <c r="U110" s="2"/>
     </row>
-    <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>11</v>
       </c>
@@ -10994,7 +11024,7 @@
       <c r="T111" s="2"/>
       <c r="U111" s="2"/>
     </row>
-    <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>11</v>
       </c>
@@ -11044,7 +11074,7 @@
       <c r="T112" s="2"/>
       <c r="U112" s="2"/>
     </row>
-    <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>11</v>
       </c>
@@ -11094,7 +11124,7 @@
       <c r="T113" s="2"/>
       <c r="U113" s="2"/>
     </row>
-    <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>11</v>
       </c>
@@ -11144,7 +11174,7 @@
       <c r="T114" s="2"/>
       <c r="U114" s="2"/>
     </row>
-    <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>11</v>
       </c>
@@ -11194,7 +11224,7 @@
       <c r="T115" s="2"/>
       <c r="U115" s="2"/>
     </row>
-    <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>11</v>
       </c>
@@ -11244,7 +11274,7 @@
       <c r="T116" s="2"/>
       <c r="U116" s="2"/>
     </row>
-    <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>11</v>
       </c>
@@ -11294,7 +11324,7 @@
       <c r="T117" s="2"/>
       <c r="U117" s="2"/>
     </row>
-    <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>11</v>
       </c>
@@ -11344,7 +11374,7 @@
       <c r="T118" s="2"/>
       <c r="U118" s="2"/>
     </row>
-    <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>11</v>
       </c>
@@ -11394,7 +11424,7 @@
       <c r="T119" s="2"/>
       <c r="U119" s="2"/>
     </row>
-    <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>11</v>
       </c>
@@ -11444,7 +11474,7 @@
       <c r="T120" s="2"/>
       <c r="U120" s="2"/>
     </row>
-    <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>11</v>
       </c>
@@ -11494,7 +11524,7 @@
       <c r="T121" s="2"/>
       <c r="U121" s="2"/>
     </row>
-    <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>11</v>
       </c>
@@ -11718,7 +11748,7 @@
       <c r="T125" s="2"/>
       <c r="U125" s="2"/>
     </row>
-    <row r="126" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>11</v>
       </c>
@@ -11768,7 +11798,7 @@
       <c r="T126" s="2"/>
       <c r="U126" s="2"/>
     </row>
-    <row r="127" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>11</v>
       </c>
@@ -11794,7 +11824,7 @@
         <v>281</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M127" s="2" t="s">
         <v>16</v>
@@ -11818,7 +11848,7 @@
       <c r="T127" s="2"/>
       <c r="U127" s="2"/>
     </row>
-    <row r="128" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>11</v>
       </c>
@@ -11868,7 +11898,7 @@
       <c r="T128" s="2"/>
       <c r="U128" s="2"/>
     </row>
-    <row r="129" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>11</v>
       </c>
@@ -11894,7 +11924,7 @@
         <v>288</v>
       </c>
       <c r="L129" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M129" s="2" t="s">
         <v>16</v>
@@ -11918,7 +11948,7 @@
       <c r="T129" s="2"/>
       <c r="U129" s="2"/>
     </row>
-    <row r="130" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>11</v>
       </c>
@@ -11968,7 +11998,7 @@
       <c r="T130" s="2"/>
       <c r="U130" s="2"/>
     </row>
-    <row r="131" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>11</v>
       </c>
@@ -12018,7 +12048,7 @@
       <c r="T131" s="2"/>
       <c r="U131" s="2"/>
     </row>
-    <row r="132" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>11</v>
       </c>
@@ -12068,7 +12098,7 @@
       <c r="T132" s="2"/>
       <c r="U132" s="2"/>
     </row>
-    <row r="133" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>11</v>
       </c>
@@ -12094,7 +12124,7 @@
         <v>299</v>
       </c>
       <c r="L133" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M133" s="2" t="s">
         <v>16</v>
@@ -12118,7 +12148,7 @@
       <c r="T133" s="2"/>
       <c r="U133" s="2"/>
     </row>
-    <row r="134" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>11</v>
       </c>
@@ -12168,7 +12198,7 @@
       <c r="T134" s="2"/>
       <c r="U134" s="2"/>
     </row>
-    <row r="135" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>11</v>
       </c>
@@ -12194,7 +12224,7 @@
         <v>341</v>
       </c>
       <c r="L135" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M135" s="2" t="s">
         <v>16</v>
@@ -12218,7 +12248,7 @@
       <c r="T135" s="2"/>
       <c r="U135" s="2"/>
     </row>
-    <row r="136" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>11</v>
       </c>
@@ -12268,7 +12298,7 @@
       <c r="T136" s="2"/>
       <c r="U136" s="2"/>
     </row>
-    <row r="137" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>11</v>
       </c>
@@ -12318,7 +12348,7 @@
       <c r="T137" s="2"/>
       <c r="U137" s="2"/>
     </row>
-    <row r="138" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>11</v>
       </c>
@@ -12368,7 +12398,7 @@
       <c r="T138" s="2"/>
       <c r="U138" s="2"/>
     </row>
-    <row r="139" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>11</v>
       </c>
@@ -12418,7 +12448,7 @@
       <c r="T139" s="2"/>
       <c r="U139" s="2"/>
     </row>
-    <row r="140" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>11</v>
       </c>
@@ -12468,7 +12498,7 @@
       <c r="T140" s="2"/>
       <c r="U140" s="2"/>
     </row>
-    <row r="141" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>11</v>
       </c>
@@ -12518,7 +12548,7 @@
       <c r="T141" s="2"/>
       <c r="U141" s="2"/>
     </row>
-    <row r="142" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>11</v>
       </c>
@@ -12544,7 +12574,7 @@
         <v>13</v>
       </c>
       <c r="L142" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M142" s="2" t="s">
         <v>16</v>
@@ -12568,7 +12598,7 @@
       <c r="T142" s="2"/>
       <c r="U142" s="2"/>
     </row>
-    <row r="143" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>11</v>
       </c>
@@ -12594,7 +12624,7 @@
         <v>420</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M143" s="2" t="s">
         <v>16</v>
@@ -12618,7 +12648,7 @@
       <c r="T143" s="2"/>
       <c r="U143" s="2"/>
     </row>
-    <row r="144" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>11</v>
       </c>
@@ -12644,7 +12674,7 @@
         <v>423</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M144" s="2" t="s">
         <v>16</v>
@@ -12668,7 +12698,7 @@
       <c r="T144" s="2"/>
       <c r="U144" s="2"/>
     </row>
-    <row r="145" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>11</v>
       </c>
@@ -12718,7 +12748,7 @@
       <c r="T145" s="2"/>
       <c r="U145" s="2"/>
     </row>
-    <row r="146" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>11</v>
       </c>
@@ -12768,7 +12798,7 @@
       <c r="T146" s="2"/>
       <c r="U146" s="2"/>
     </row>
-    <row r="147" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>11</v>
       </c>
@@ -12818,7 +12848,7 @@
       <c r="T147" s="2"/>
       <c r="U147" s="2"/>
     </row>
-    <row r="148" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>11</v>
       </c>
@@ -12868,7 +12898,7 @@
       <c r="T148" s="2"/>
       <c r="U148" s="2"/>
     </row>
-    <row r="149" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>11</v>
       </c>
@@ -12918,7 +12948,7 @@
       <c r="T149" s="2"/>
       <c r="U149" s="2"/>
     </row>
-    <row r="150" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>11</v>
       </c>
@@ -12968,7 +12998,7 @@
       <c r="T150" s="2"/>
       <c r="U150" s="2"/>
     </row>
-    <row r="151" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>11</v>
       </c>
@@ -13018,7 +13048,7 @@
       <c r="T151" s="2"/>
       <c r="U151" s="2"/>
     </row>
-    <row r="152" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>11</v>
       </c>
@@ -13068,7 +13098,7 @@
       <c r="T152" s="2"/>
       <c r="U152" s="2"/>
     </row>
-    <row r="153" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>11</v>
       </c>
@@ -13118,7 +13148,7 @@
       <c r="T153" s="2"/>
       <c r="U153" s="2"/>
     </row>
-    <row r="154" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>11</v>
       </c>
@@ -13168,7 +13198,7 @@
       <c r="T154" s="2"/>
       <c r="U154" s="2"/>
     </row>
-    <row r="155" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>11</v>
       </c>
@@ -13218,7 +13248,7 @@
       <c r="T155" s="2"/>
       <c r="U155" s="2"/>
     </row>
-    <row r="156" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>11</v>
       </c>
@@ -13268,7 +13298,7 @@
       <c r="T156" s="2"/>
       <c r="U156" s="2"/>
     </row>
-    <row r="157" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>11</v>
       </c>
@@ -13318,7 +13348,7 @@
       <c r="T157" s="2"/>
       <c r="U157" s="2"/>
     </row>
-    <row r="158" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>11</v>
       </c>
@@ -13368,7 +13398,7 @@
       <c r="T158" s="2"/>
       <c r="U158" s="2"/>
     </row>
-    <row r="159" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>11</v>
       </c>
@@ -13418,7 +13448,7 @@
       <c r="T159" s="2"/>
       <c r="U159" s="2"/>
     </row>
-    <row r="160" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>11</v>
       </c>
@@ -13468,7 +13498,7 @@
       <c r="T160" s="2"/>
       <c r="U160" s="2"/>
     </row>
-    <row r="161" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>11</v>
       </c>
@@ -13518,7 +13548,7 @@
       <c r="T161" s="2"/>
       <c r="U161" s="2"/>
     </row>
-    <row r="162" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>11</v>
       </c>
@@ -13568,7 +13598,7 @@
       <c r="T162" s="2"/>
       <c r="U162" s="2"/>
     </row>
-    <row r="163" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>11</v>
       </c>
@@ -13618,7 +13648,7 @@
       <c r="T163" s="2"/>
       <c r="U163" s="2"/>
     </row>
-    <row r="164" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>11</v>
       </c>
@@ -13668,7 +13698,7 @@
       <c r="T164" s="2"/>
       <c r="U164" s="2"/>
     </row>
-    <row r="165" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>11</v>
       </c>
@@ -13718,7 +13748,7 @@
       <c r="T165" s="2"/>
       <c r="U165" s="2"/>
     </row>
-    <row r="166" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>11</v>
       </c>
@@ -13768,7 +13798,7 @@
       <c r="T166" s="2"/>
       <c r="U166" s="2"/>
     </row>
-    <row r="167" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>11</v>
       </c>
@@ -13818,7 +13848,7 @@
       <c r="T167" s="2"/>
       <c r="U167" s="2"/>
     </row>
-    <row r="168" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>11</v>
       </c>
@@ -13868,7 +13898,7 @@
       <c r="T168" s="2"/>
       <c r="U168" s="2"/>
     </row>
-    <row r="169" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>11</v>
       </c>
@@ -13918,7 +13948,7 @@
       <c r="T169" s="2"/>
       <c r="U169" s="2"/>
     </row>
-    <row r="170" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>11</v>
       </c>
@@ -13968,7 +13998,7 @@
       <c r="T170" s="2"/>
       <c r="U170" s="2"/>
     </row>
-    <row r="171" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>11</v>
       </c>
@@ -14018,7 +14048,7 @@
       <c r="T171" s="2"/>
       <c r="U171" s="2"/>
     </row>
-    <row r="172" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>11</v>
       </c>
@@ -14068,7 +14098,7 @@
       <c r="T172" s="2"/>
       <c r="U172" s="2"/>
     </row>
-    <row r="173" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>11</v>
       </c>
@@ -14118,7 +14148,7 @@
       <c r="T173" s="2"/>
       <c r="U173" s="2"/>
     </row>
-    <row r="174" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>11</v>
       </c>
@@ -14168,7 +14198,7 @@
       <c r="T174" s="2"/>
       <c r="U174" s="2"/>
     </row>
-    <row r="175" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>11</v>
       </c>
@@ -14508,7 +14538,7 @@
       <c r="T180" s="2"/>
       <c r="U180" s="2"/>
     </row>
-    <row r="181" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>11</v>
       </c>
@@ -14534,7 +14564,7 @@
         <v>792</v>
       </c>
       <c r="L181" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M181" s="2" t="s">
         <v>16</v>
@@ -14558,7 +14588,7 @@
       <c r="T181" s="2"/>
       <c r="U181" s="2"/>
     </row>
-    <row r="182" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>11</v>
       </c>
@@ -14608,7 +14638,7 @@
       <c r="T182" s="2"/>
       <c r="U182" s="2"/>
     </row>
-    <row r="183" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>11</v>
       </c>
@@ -14658,7 +14688,7 @@
       <c r="T183" s="2"/>
       <c r="U183" s="2"/>
     </row>
-    <row r="184" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>11</v>
       </c>
@@ -14708,7 +14738,7 @@
       <c r="T184" s="2"/>
       <c r="U184" s="2"/>
     </row>
-    <row r="185" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>11</v>
       </c>
@@ -14758,7 +14788,7 @@
       <c r="T185" s="2"/>
       <c r="U185" s="2"/>
     </row>
-    <row r="186" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>11</v>
       </c>
@@ -14808,7 +14838,7 @@
       <c r="T186" s="2"/>
       <c r="U186" s="2"/>
     </row>
-    <row r="187" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>11</v>
       </c>
@@ -14834,7 +14864,7 @@
         <v>809</v>
       </c>
       <c r="L187" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M187" s="2" t="s">
         <v>16</v>
@@ -14858,7 +14888,7 @@
       <c r="T187" s="2"/>
       <c r="U187" s="2"/>
     </row>
-    <row r="188" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>11</v>
       </c>
@@ -14908,7 +14938,7 @@
       <c r="T188" s="2"/>
       <c r="U188" s="2"/>
     </row>
-    <row r="189" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>11</v>
       </c>
@@ -14934,7 +14964,7 @@
         <v>13</v>
       </c>
       <c r="L189" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M189" s="2" t="s">
         <v>16</v>
@@ -14958,7 +14988,7 @@
       <c r="T189" s="2"/>
       <c r="U189" s="2"/>
     </row>
-    <row r="190" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>11</v>
       </c>
@@ -14984,7 +15014,7 @@
         <v>822</v>
       </c>
       <c r="L190" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M190" s="2" t="s">
         <v>16</v>
@@ -15008,7 +15038,7 @@
       <c r="T190" s="2"/>
       <c r="U190" s="2"/>
     </row>
-    <row r="191" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>11</v>
       </c>
@@ -15034,7 +15064,7 @@
         <v>824</v>
       </c>
       <c r="L191" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M191" s="2" t="s">
         <v>16</v>
@@ -15058,7 +15088,7 @@
       <c r="T191" s="2"/>
       <c r="U191" s="2"/>
     </row>
-    <row r="192" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>11</v>
       </c>
@@ -15108,7 +15138,7 @@
       <c r="T192" s="2"/>
       <c r="U192" s="2"/>
     </row>
-    <row r="193" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>11</v>
       </c>
@@ -15158,7 +15188,7 @@
       <c r="T193" s="2"/>
       <c r="U193" s="2"/>
     </row>
-    <row r="194" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>11</v>
       </c>
@@ -15208,7 +15238,7 @@
       <c r="T194" s="2"/>
       <c r="U194" s="2"/>
     </row>
-    <row r="195" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>11</v>
       </c>
@@ -15258,7 +15288,7 @@
       <c r="T195" s="2"/>
       <c r="U195" s="2"/>
     </row>
-    <row r="196" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>11</v>
       </c>
@@ -15308,7 +15338,7 @@
       <c r="T196" s="2"/>
       <c r="U196" s="2"/>
     </row>
-    <row r="197" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>11</v>
       </c>
@@ -15358,7 +15388,7 @@
       <c r="T197" s="2"/>
       <c r="U197" s="2"/>
     </row>
-    <row r="198" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>11</v>
       </c>
@@ -15408,7 +15438,7 @@
       <c r="T198" s="2"/>
       <c r="U198" s="2"/>
     </row>
-    <row r="199" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>11</v>
       </c>
@@ -15458,7 +15488,7 @@
       <c r="T199" s="2"/>
       <c r="U199" s="2"/>
     </row>
-    <row r="200" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>11</v>
       </c>
@@ -15508,7 +15538,7 @@
       <c r="T200" s="2"/>
       <c r="U200" s="2"/>
     </row>
-    <row r="201" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>11</v>
       </c>
@@ -15558,7 +15588,7 @@
       <c r="T201" s="2"/>
       <c r="U201" s="2"/>
     </row>
-    <row r="202" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>11</v>
       </c>
@@ -15608,7 +15638,7 @@
       <c r="T202" s="2"/>
       <c r="U202" s="2"/>
     </row>
-    <row r="203" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>11</v>
       </c>
@@ -15634,7 +15664,7 @@
         <v>968</v>
       </c>
       <c r="L203" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M203" s="2" t="s">
         <v>16</v>
@@ -15658,7 +15688,7 @@
       <c r="T203" s="2"/>
       <c r="U203" s="2"/>
     </row>
-    <row r="204" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>11</v>
       </c>
@@ -15708,7 +15738,7 @@
       <c r="T204" s="2"/>
       <c r="U204" s="2"/>
     </row>
-    <row r="205" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>11</v>
       </c>
@@ -15758,7 +15788,7 @@
       <c r="T205" s="2"/>
       <c r="U205" s="2"/>
     </row>
-    <row r="206" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>11</v>
       </c>
@@ -15808,7 +15838,7 @@
       <c r="T206" s="2"/>
       <c r="U206" s="2"/>
     </row>
-    <row r="207" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>11</v>
       </c>
@@ -15858,7 +15888,7 @@
       <c r="T207" s="2"/>
       <c r="U207" s="2"/>
     </row>
-    <row r="208" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>11</v>
       </c>
@@ -15908,7 +15938,7 @@
       <c r="T208" s="2"/>
       <c r="U208" s="2"/>
     </row>
-    <row r="209" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>11</v>
       </c>
@@ -15934,7 +15964,7 @@
         <v>983</v>
       </c>
       <c r="L209" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M209" s="2" t="s">
         <v>16</v>
@@ -15958,7 +15988,7 @@
       <c r="T209" s="2"/>
       <c r="U209" s="2"/>
     </row>
-    <row r="210" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>11</v>
       </c>
@@ -16008,7 +16038,7 @@
       <c r="T210" s="2"/>
       <c r="U210" s="2"/>
     </row>
-    <row r="211" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>11</v>
       </c>
@@ -16034,7 +16064,7 @@
         <v>13</v>
       </c>
       <c r="L211" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M211" s="2" t="s">
         <v>16</v>
@@ -16058,7 +16088,7 @@
       <c r="T211" s="2"/>
       <c r="U211" s="2"/>
     </row>
-    <row r="212" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>11</v>
       </c>
@@ -16084,7 +16114,7 @@
         <v>993</v>
       </c>
       <c r="L212" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M212" s="2" t="s">
         <v>16</v>
@@ -16108,7 +16138,7 @@
       <c r="T212" s="2"/>
       <c r="U212" s="2"/>
     </row>
-    <row r="213" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>11</v>
       </c>
@@ -16134,7 +16164,7 @@
         <v>995</v>
       </c>
       <c r="L213" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M213" s="2" t="s">
         <v>16</v>
@@ -16158,7 +16188,7 @@
       <c r="T213" s="2"/>
       <c r="U213" s="2"/>
     </row>
-    <row r="214" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>11</v>
       </c>
@@ -16208,7 +16238,7 @@
       <c r="T214" s="2"/>
       <c r="U214" s="2"/>
     </row>
-    <row r="215" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>11</v>
       </c>
@@ -16258,7 +16288,7 @@
       <c r="T215" s="2"/>
       <c r="U215" s="2"/>
     </row>
-    <row r="216" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>11</v>
       </c>
@@ -16308,7 +16338,7 @@
       <c r="T216" s="2"/>
       <c r="U216" s="2"/>
     </row>
-    <row r="217" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>11</v>
       </c>
@@ -16358,7 +16388,7 @@
       <c r="T217" s="2"/>
       <c r="U217" s="2"/>
     </row>
-    <row r="218" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>11</v>
       </c>
@@ -16408,7 +16438,7 @@
       <c r="T218" s="2"/>
       <c r="U218" s="2"/>
     </row>
-    <row r="219" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>11</v>
       </c>
@@ -16458,7 +16488,7 @@
       <c r="T219" s="2"/>
       <c r="U219" s="2"/>
     </row>
-    <row r="220" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>11</v>
       </c>
@@ -16508,7 +16538,7 @@
       <c r="T220" s="2"/>
       <c r="U220" s="2"/>
     </row>
-    <row r="221" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>11</v>
       </c>
@@ -16558,7 +16588,7 @@
       <c r="T221" s="2"/>
       <c r="U221" s="2"/>
     </row>
-    <row r="222" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>11</v>
       </c>
@@ -16608,7 +16638,7 @@
       <c r="T222" s="2"/>
       <c r="U222" s="2"/>
     </row>
-    <row r="223" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>11</v>
       </c>
@@ -16658,7 +16688,7 @@
       <c r="T223" s="2"/>
       <c r="U223" s="2"/>
     </row>
-    <row r="224" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>11</v>
       </c>
@@ -16684,7 +16714,7 @@
         <v>1086</v>
       </c>
       <c r="L224" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M224" s="2" t="s">
         <v>16</v>
@@ -16708,7 +16738,7 @@
       <c r="T224" s="2"/>
       <c r="U224" s="2"/>
     </row>
-    <row r="225" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>11</v>
       </c>
@@ -16758,7 +16788,7 @@
       <c r="T225" s="2"/>
       <c r="U225" s="2"/>
     </row>
-    <row r="226" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>11</v>
       </c>
@@ -16808,7 +16838,7 @@
       <c r="T226" s="2"/>
       <c r="U226" s="2"/>
     </row>
-    <row r="227" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>11</v>
       </c>
@@ -16858,7 +16888,7 @@
       <c r="T227" s="2"/>
       <c r="U227" s="2"/>
     </row>
-    <row r="228" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>11</v>
       </c>
@@ -16908,7 +16938,7 @@
       <c r="T228" s="2"/>
       <c r="U228" s="2"/>
     </row>
-    <row r="229" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>11</v>
       </c>
@@ -16958,7 +16988,7 @@
       <c r="T229" s="2"/>
       <c r="U229" s="2"/>
     </row>
-    <row r="230" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>11</v>
       </c>
@@ -16984,7 +17014,7 @@
         <v>1099</v>
       </c>
       <c r="L230" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M230" s="2" t="s">
         <v>16</v>
@@ -17008,7 +17038,7 @@
       <c r="T230" s="2"/>
       <c r="U230" s="2"/>
     </row>
-    <row r="231" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>11</v>
       </c>
@@ -17058,7 +17088,7 @@
       <c r="T231" s="2"/>
       <c r="U231" s="2"/>
     </row>
-    <row r="232" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>11</v>
       </c>
@@ -17084,7 +17114,7 @@
         <v>1103</v>
       </c>
       <c r="L232" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M232" s="2" t="s">
         <v>16</v>
@@ -17108,7 +17138,7 @@
       <c r="T232" s="2"/>
       <c r="U232" s="2"/>
     </row>
-    <row r="233" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>11</v>
       </c>
@@ -17134,7 +17164,7 @@
         <v>1105</v>
       </c>
       <c r="L233" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M233" s="2" t="s">
         <v>16</v>
@@ -17158,7 +17188,7 @@
       <c r="T233" s="2"/>
       <c r="U233" s="2"/>
     </row>
-    <row r="234" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>11</v>
       </c>
@@ -17208,7 +17238,7 @@
       <c r="T234" s="2"/>
       <c r="U234" s="2"/>
     </row>
-    <row r="235" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>11</v>
       </c>
@@ -17258,7 +17288,7 @@
       <c r="T235" s="2"/>
       <c r="U235" s="2"/>
     </row>
-    <row r="236" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>11</v>
       </c>
@@ -17308,7 +17338,7 @@
       <c r="T236" s="2"/>
       <c r="U236" s="2"/>
     </row>
-    <row r="237" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>11</v>
       </c>
@@ -17358,7 +17388,7 @@
       <c r="T237" s="2"/>
       <c r="U237" s="2"/>
     </row>
-    <row r="238" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>11</v>
       </c>
@@ -17408,7 +17438,7 @@
       <c r="T238" s="2"/>
       <c r="U238" s="2"/>
     </row>
-    <row r="239" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>11</v>
       </c>
@@ -17458,7 +17488,7 @@
       <c r="T239" s="2"/>
       <c r="U239" s="2"/>
     </row>
-    <row r="240" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>11</v>
       </c>
@@ -17508,7 +17538,7 @@
       <c r="T240" s="2"/>
       <c r="U240" s="2"/>
     </row>
-    <row r="241" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>11</v>
       </c>
@@ -17558,7 +17588,7 @@
       <c r="T241" s="2"/>
       <c r="U241" s="2"/>
     </row>
-    <row r="242" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>11</v>
       </c>
@@ -17608,7 +17638,7 @@
       <c r="T242" s="2"/>
       <c r="U242" s="2"/>
     </row>
-    <row r="243" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>11</v>
       </c>
@@ -17658,7 +17688,7 @@
       <c r="T243" s="2"/>
       <c r="U243" s="2"/>
     </row>
-    <row r="244" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>11</v>
       </c>
@@ -17708,7 +17738,7 @@
       <c r="T244" s="2"/>
       <c r="U244" s="2"/>
     </row>
-    <row r="245" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>11</v>
       </c>
@@ -17758,7 +17788,7 @@
       <c r="T245" s="2"/>
       <c r="U245" s="2"/>
     </row>
-    <row r="246" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>11</v>
       </c>
@@ -17808,7 +17838,7 @@
       <c r="T246" s="2"/>
       <c r="U246" s="2"/>
     </row>
-    <row r="247" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>11</v>
       </c>
@@ -17858,7 +17888,7 @@
       <c r="T247" s="2"/>
       <c r="U247" s="2"/>
     </row>
-    <row r="248" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>11</v>
       </c>
@@ -17884,7 +17914,7 @@
         <v>1169</v>
       </c>
       <c r="L248" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M248" s="2" t="s">
         <v>16</v>
@@ -17908,7 +17938,7 @@
       <c r="T248" s="2"/>
       <c r="U248" s="2"/>
     </row>
-    <row r="249" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>11</v>
       </c>
@@ -17958,7 +17988,7 @@
       <c r="T249" s="2"/>
       <c r="U249" s="2"/>
     </row>
-    <row r="250" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>11</v>
       </c>
@@ -18008,7 +18038,7 @@
       <c r="T250" s="2"/>
       <c r="U250" s="2"/>
     </row>
-    <row r="251" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>11</v>
       </c>
@@ -18058,7 +18088,7 @@
       <c r="T251" s="2"/>
       <c r="U251" s="2"/>
     </row>
-    <row r="252" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>11</v>
       </c>
@@ -18108,7 +18138,7 @@
       <c r="T252" s="2"/>
       <c r="U252" s="2"/>
     </row>
-    <row r="253" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>11</v>
       </c>
@@ -18158,7 +18188,7 @@
       <c r="T253" s="2"/>
       <c r="U253" s="2"/>
     </row>
-    <row r="254" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>11</v>
       </c>
@@ -18208,7 +18238,7 @@
       <c r="T254" s="2"/>
       <c r="U254" s="2"/>
     </row>
-    <row r="255" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>11</v>
       </c>
@@ -18258,7 +18288,7 @@
       <c r="T255" s="2"/>
       <c r="U255" s="2"/>
     </row>
-    <row r="256" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>11</v>
       </c>
@@ -18308,7 +18338,7 @@
       <c r="T256" s="2"/>
       <c r="U256" s="2"/>
     </row>
-    <row r="257" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>11</v>
       </c>
@@ -18358,7 +18388,7 @@
       <c r="T257" s="2"/>
       <c r="U257" s="2"/>
     </row>
-    <row r="258" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>11</v>
       </c>
@@ -18408,7 +18438,7 @@
       <c r="T258" s="2"/>
       <c r="U258" s="2"/>
     </row>
-    <row r="259" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>11</v>
       </c>
@@ -18458,7 +18488,7 @@
       <c r="T259" s="2"/>
       <c r="U259" s="2"/>
     </row>
-    <row r="260" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>11</v>
       </c>
@@ -18508,7 +18538,7 @@
       <c r="T260" s="2"/>
       <c r="U260" s="2"/>
     </row>
-    <row r="261" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>11</v>
       </c>
@@ -18558,7 +18588,7 @@
       <c r="T261" s="2"/>
       <c r="U261" s="2"/>
     </row>
-    <row r="262" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>11</v>
       </c>
@@ -18608,7 +18638,7 @@
       <c r="T262" s="2"/>
       <c r="U262" s="2"/>
     </row>
-    <row r="263" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>11</v>
       </c>
@@ -18658,7 +18688,7 @@
       <c r="T263" s="2"/>
       <c r="U263" s="2"/>
     </row>
-    <row r="264" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>11</v>
       </c>
@@ -18708,7 +18738,7 @@
       <c r="T264" s="2"/>
       <c r="U264" s="2"/>
     </row>
-    <row r="265" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>11</v>
       </c>
@@ -18758,7 +18788,7 @@
       <c r="T265" s="2"/>
       <c r="U265" s="2"/>
     </row>
-    <row r="266" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>11</v>
       </c>
@@ -18808,7 +18838,7 @@
       <c r="T266" s="2"/>
       <c r="U266" s="2"/>
     </row>
-    <row r="267" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>11</v>
       </c>
@@ -18858,7 +18888,7 @@
       <c r="T267" s="2"/>
       <c r="U267" s="2"/>
     </row>
-    <row r="268" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>11</v>
       </c>
@@ -18908,7 +18938,7 @@
       <c r="T268" s="2"/>
       <c r="U268" s="2"/>
     </row>
-    <row r="269" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>11</v>
       </c>
@@ -18958,7 +18988,7 @@
       <c r="T269" s="2"/>
       <c r="U269" s="2"/>
     </row>
-    <row r="270" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>11</v>
       </c>
@@ -19008,7 +19038,7 @@
       <c r="T270" s="2"/>
       <c r="U270" s="2"/>
     </row>
-    <row r="271" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>11</v>
       </c>
@@ -19058,7 +19088,7 @@
       <c r="T271" s="2"/>
       <c r="U271" s="2"/>
     </row>
-    <row r="272" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>11</v>
       </c>
@@ -19108,7 +19138,7 @@
       <c r="T272" s="2"/>
       <c r="U272" s="2"/>
     </row>
-    <row r="273" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>11</v>
       </c>
@@ -19158,7 +19188,7 @@
       <c r="T273" s="2"/>
       <c r="U273" s="2"/>
     </row>
-    <row r="274" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>11</v>
       </c>
@@ -19208,7 +19238,7 @@
       <c r="T274" s="2"/>
       <c r="U274" s="2"/>
     </row>
-    <row r="275" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>11</v>
       </c>
@@ -19258,7 +19288,7 @@
       <c r="T275" s="2"/>
       <c r="U275" s="2"/>
     </row>
-    <row r="276" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>11</v>
       </c>
@@ -19308,7 +19338,7 @@
       <c r="T276" s="2"/>
       <c r="U276" s="2"/>
     </row>
-    <row r="277" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>11</v>
       </c>
@@ -19358,7 +19388,7 @@
       <c r="T277" s="2"/>
       <c r="U277" s="2"/>
     </row>
-    <row r="278" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>11</v>
       </c>
@@ -19408,7 +19438,7 @@
       <c r="T278" s="2"/>
       <c r="U278" s="2"/>
     </row>
-    <row r="279" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>11</v>
       </c>
@@ -19458,7 +19488,7 @@
       <c r="T279" s="2"/>
       <c r="U279" s="2"/>
     </row>
-    <row r="280" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>11</v>
       </c>
@@ -19508,7 +19538,7 @@
       <c r="T280" s="2"/>
       <c r="U280" s="2"/>
     </row>
-    <row r="281" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>11</v>
       </c>
@@ -19558,7 +19588,7 @@
       <c r="T281" s="2"/>
       <c r="U281" s="2"/>
     </row>
-    <row r="282" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>11</v>
       </c>
@@ -19608,7 +19638,7 @@
       <c r="T282" s="2"/>
       <c r="U282" s="2"/>
     </row>
-    <row r="283" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>11</v>
       </c>
@@ -19658,7 +19688,7 @@
       <c r="T283" s="2"/>
       <c r="U283" s="2"/>
     </row>
-    <row r="284" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>11</v>
       </c>
@@ -19708,7 +19738,7 @@
       <c r="T284" s="2"/>
       <c r="U284" s="2"/>
     </row>
-    <row r="285" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>11</v>
       </c>
@@ -19758,7 +19788,7 @@
       <c r="T285" s="2"/>
       <c r="U285" s="2"/>
     </row>
-    <row r="286" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>11</v>
       </c>
@@ -19808,7 +19838,7 @@
       <c r="T286" s="2"/>
       <c r="U286" s="2"/>
     </row>
-    <row r="287" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>11</v>
       </c>
@@ -19858,7 +19888,7 @@
       <c r="T287" s="2"/>
       <c r="U287" s="2"/>
     </row>
-    <row r="288" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>11</v>
       </c>
@@ -19908,7 +19938,7 @@
       <c r="T288" s="2"/>
       <c r="U288" s="2"/>
     </row>
-    <row r="289" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>11</v>
       </c>
@@ -19958,7 +19988,7 @@
       <c r="T289" s="2"/>
       <c r="U289" s="2"/>
     </row>
-    <row r="290" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>11</v>
       </c>
@@ -20008,7 +20038,7 @@
       <c r="T290" s="2"/>
       <c r="U290" s="2"/>
     </row>
-    <row r="291" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>11</v>
       </c>
@@ -20058,7 +20088,7 @@
       <c r="T291" s="2"/>
       <c r="U291" s="2"/>
     </row>
-    <row r="292" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>11</v>
       </c>
@@ -20108,7 +20138,7 @@
       <c r="T292" s="2"/>
       <c r="U292" s="2"/>
     </row>
-    <row r="293" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>11</v>
       </c>
@@ -20158,7 +20188,7 @@
       <c r="T293" s="2"/>
       <c r="U293" s="2"/>
     </row>
-    <row r="294" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>11</v>
       </c>
@@ -20208,7 +20238,7 @@
       <c r="T294" s="2"/>
       <c r="U294" s="2"/>
     </row>
-    <row r="295" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>11</v>
       </c>
@@ -20258,7 +20288,7 @@
       <c r="T295" s="2"/>
       <c r="U295" s="2"/>
     </row>
-    <row r="296" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>11</v>
       </c>
@@ -20308,7 +20338,7 @@
       <c r="T296" s="2"/>
       <c r="U296" s="2"/>
     </row>
-    <row r="297" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>11</v>
       </c>
@@ -20358,7 +20388,7 @@
       <c r="T297" s="2"/>
       <c r="U297" s="2"/>
     </row>
-    <row r="298" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>11</v>
       </c>
@@ -20408,7 +20438,7 @@
       <c r="T298" s="2"/>
       <c r="U298" s="2"/>
     </row>
-    <row r="299" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>11</v>
       </c>
@@ -20458,7 +20488,7 @@
       <c r="T299" s="2"/>
       <c r="U299" s="2"/>
     </row>
-    <row r="300" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>11</v>
       </c>
@@ -20508,7 +20538,7 @@
       <c r="T300" s="2"/>
       <c r="U300" s="2"/>
     </row>
-    <row r="301" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>11</v>
       </c>
@@ -20558,7 +20588,7 @@
       <c r="T301" s="2"/>
       <c r="U301" s="2"/>
     </row>
-    <row r="302" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>11</v>
       </c>
@@ -20608,7 +20638,7 @@
       <c r="T302" s="2"/>
       <c r="U302" s="2"/>
     </row>
-    <row r="303" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>11</v>
       </c>
@@ -20658,7 +20688,7 @@
       <c r="T303" s="2"/>
       <c r="U303" s="2"/>
     </row>
-    <row r="304" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>11</v>
       </c>
@@ -20708,7 +20738,7 @@
       <c r="T304" s="2"/>
       <c r="U304" s="2"/>
     </row>
-    <row r="305" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>11</v>
       </c>
@@ -20758,7 +20788,7 @@
       <c r="T305" s="2"/>
       <c r="U305" s="2"/>
     </row>
-    <row r="306" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>11</v>
       </c>
@@ -20808,7 +20838,7 @@
       <c r="T306" s="2"/>
       <c r="U306" s="2"/>
     </row>
-    <row r="307" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>11</v>
       </c>
@@ -20916,7 +20946,7 @@
       <c r="T308" s="2"/>
       <c r="U308" s="2"/>
     </row>
-    <row r="309" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>11</v>
       </c>
@@ -20942,7 +20972,7 @@
         <v>307</v>
       </c>
       <c r="L309" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M309" s="2" t="s">
         <v>16</v>
@@ -20966,7 +20996,7 @@
       <c r="T309" s="2"/>
       <c r="U309" s="2"/>
     </row>
-    <row r="310" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>11</v>
       </c>
@@ -21132,7 +21162,7 @@
       <c r="T312" s="2"/>
       <c r="U312" s="2"/>
     </row>
-    <row r="313" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>11</v>
       </c>
@@ -21820,7 +21850,7 @@
       <c r="T324" s="2"/>
       <c r="U324" s="2"/>
     </row>
-    <row r="325" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>11</v>
       </c>
@@ -22044,7 +22074,7 @@
       <c r="T328" s="2"/>
       <c r="U328" s="2"/>
     </row>
-    <row r="329" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>11</v>
       </c>
@@ -22268,7 +22298,7 @@
       <c r="T332" s="2"/>
       <c r="U332" s="2"/>
     </row>
-    <row r="333" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>11</v>
       </c>
@@ -22318,7 +22348,7 @@
       <c r="T333" s="2"/>
       <c r="U333" s="2"/>
     </row>
-    <row r="334" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>11</v>
       </c>
@@ -22368,7 +22398,7 @@
       <c r="T334" s="2"/>
       <c r="U334" s="2"/>
     </row>
-    <row r="335" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>11</v>
       </c>
@@ -22418,7 +22448,7 @@
       <c r="T335" s="2"/>
       <c r="U335" s="2"/>
     </row>
-    <row r="336" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>11</v>
       </c>
@@ -22468,7 +22498,7 @@
       <c r="T336" s="2"/>
       <c r="U336" s="2"/>
     </row>
-    <row r="337" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>11</v>
       </c>
@@ -22518,7 +22548,7 @@
       <c r="T337" s="2"/>
       <c r="U337" s="2"/>
     </row>
-    <row r="338" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>11</v>
       </c>
@@ -22568,7 +22598,7 @@
       <c r="T338" s="2"/>
       <c r="U338" s="2"/>
     </row>
-    <row r="339" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>11</v>
       </c>
@@ -22618,7 +22648,7 @@
       <c r="T339" s="2"/>
       <c r="U339" s="2"/>
     </row>
-    <row r="340" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>11</v>
       </c>
@@ -22668,7 +22698,7 @@
       <c r="T340" s="2"/>
       <c r="U340" s="2"/>
     </row>
-    <row r="341" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>11</v>
       </c>
@@ -22718,7 +22748,7 @@
       <c r="T341" s="2"/>
       <c r="U341" s="2"/>
     </row>
-    <row r="342" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>11</v>
       </c>
@@ -22768,7 +22798,7 @@
       <c r="T342" s="2"/>
       <c r="U342" s="2"/>
     </row>
-    <row r="343" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>11</v>
       </c>
@@ -22818,7 +22848,7 @@
       <c r="T343" s="2"/>
       <c r="U343" s="2"/>
     </row>
-    <row r="344" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>11</v>
       </c>
@@ -22868,7 +22898,7 @@
       <c r="T344" s="2"/>
       <c r="U344" s="2"/>
     </row>
-    <row r="345" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>11</v>
       </c>
@@ -22918,7 +22948,7 @@
       <c r="T345" s="2"/>
       <c r="U345" s="2"/>
     </row>
-    <row r="346" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>11</v>
       </c>
@@ -22968,7 +22998,7 @@
       <c r="T346" s="2"/>
       <c r="U346" s="2"/>
     </row>
-    <row r="347" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>11</v>
       </c>
@@ -23018,7 +23048,7 @@
       <c r="T347" s="2"/>
       <c r="U347" s="2"/>
     </row>
-    <row r="348" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>11</v>
       </c>
@@ -23068,7 +23098,7 @@
       <c r="T348" s="2"/>
       <c r="U348" s="2"/>
     </row>
-    <row r="349" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>11</v>
       </c>
@@ -23118,7 +23148,7 @@
       <c r="T349" s="2"/>
       <c r="U349" s="2"/>
     </row>
-    <row r="350" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>11</v>
       </c>
@@ -23168,7 +23198,7 @@
       <c r="T350" s="2"/>
       <c r="U350" s="2"/>
     </row>
-    <row r="351" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>11</v>
       </c>
@@ -23218,7 +23248,7 @@
       <c r="T351" s="2"/>
       <c r="U351" s="2"/>
     </row>
-    <row r="352" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>11</v>
       </c>
@@ -23268,7 +23298,7 @@
       <c r="T352" s="2"/>
       <c r="U352" s="2"/>
     </row>
-    <row r="353" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>11</v>
       </c>
@@ -23318,7 +23348,7 @@
       <c r="T353" s="2"/>
       <c r="U353" s="2"/>
     </row>
-    <row r="354" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>11</v>
       </c>
@@ -23368,7 +23398,7 @@
       <c r="T354" s="2"/>
       <c r="U354" s="2"/>
     </row>
-    <row r="355" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>11</v>
       </c>
@@ -23418,7 +23448,7 @@
       <c r="T355" s="2"/>
       <c r="U355" s="2"/>
     </row>
-    <row r="356" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>11</v>
       </c>
@@ -23468,7 +23498,7 @@
       <c r="T356" s="2"/>
       <c r="U356" s="2"/>
     </row>
-    <row r="357" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>11</v>
       </c>
@@ -23518,7 +23548,7 @@
       <c r="T357" s="2"/>
       <c r="U357" s="2"/>
     </row>
-    <row r="358" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>11</v>
       </c>
@@ -23568,7 +23598,7 @@
       <c r="T358" s="2"/>
       <c r="U358" s="2"/>
     </row>
-    <row r="359" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>11</v>
       </c>
@@ -23618,7 +23648,7 @@
       <c r="T359" s="2"/>
       <c r="U359" s="2"/>
     </row>
-    <row r="360" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>11</v>
       </c>
@@ -23668,7 +23698,7 @@
       <c r="T360" s="2"/>
       <c r="U360" s="2"/>
     </row>
-    <row r="361" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>11</v>
       </c>
@@ -23718,7 +23748,7 @@
       <c r="T361" s="2"/>
       <c r="U361" s="2"/>
     </row>
-    <row r="362" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>11</v>
       </c>
@@ -23768,7 +23798,7 @@
       <c r="T362" s="2"/>
       <c r="U362" s="2"/>
     </row>
-    <row r="363" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>11</v>
       </c>
@@ -23818,7 +23848,7 @@
       <c r="T363" s="2"/>
       <c r="U363" s="2"/>
     </row>
-    <row r="364" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>11</v>
       </c>
@@ -23868,7 +23898,7 @@
       <c r="T364" s="2"/>
       <c r="U364" s="2"/>
     </row>
-    <row r="365" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>11</v>
       </c>
@@ -23918,7 +23948,7 @@
       <c r="T365" s="2"/>
       <c r="U365" s="2"/>
     </row>
-    <row r="366" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>11</v>
       </c>
@@ -23968,7 +23998,7 @@
       <c r="T366" s="2"/>
       <c r="U366" s="2"/>
     </row>
-    <row r="367" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>11</v>
       </c>
@@ -24018,7 +24048,7 @@
       <c r="T367" s="2"/>
       <c r="U367" s="2"/>
     </row>
-    <row r="368" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>11</v>
       </c>
@@ -24068,7 +24098,7 @@
       <c r="T368" s="2"/>
       <c r="U368" s="2"/>
     </row>
-    <row r="369" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>11</v>
       </c>
@@ -24118,7 +24148,7 @@
       <c r="T369" s="2"/>
       <c r="U369" s="2"/>
     </row>
-    <row r="370" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>11</v>
       </c>
@@ -24168,7 +24198,7 @@
       <c r="T370" s="2"/>
       <c r="U370" s="2"/>
     </row>
-    <row r="371" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>11</v>
       </c>
@@ -24218,7 +24248,7 @@
       <c r="T371" s="2"/>
       <c r="U371" s="2"/>
     </row>
-    <row r="372" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>11</v>
       </c>
@@ -24268,7 +24298,7 @@
       <c r="T372" s="2"/>
       <c r="U372" s="2"/>
     </row>
-    <row r="373" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>11</v>
       </c>
@@ -24318,7 +24348,7 @@
       <c r="T373" s="2"/>
       <c r="U373" s="2"/>
     </row>
-    <row r="374" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>11</v>
       </c>
@@ -24368,7 +24398,7 @@
       <c r="T374" s="2"/>
       <c r="U374" s="2"/>
     </row>
-    <row r="375" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>11</v>
       </c>
@@ -24418,7 +24448,7 @@
       <c r="T375" s="2"/>
       <c r="U375" s="2"/>
     </row>
-    <row r="376" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>11</v>
       </c>
@@ -24468,7 +24498,7 @@
       <c r="T376" s="2"/>
       <c r="U376" s="2"/>
     </row>
-    <row r="377" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>11</v>
       </c>
@@ -24518,7 +24548,7 @@
       <c r="T377" s="2"/>
       <c r="U377" s="2"/>
     </row>
-    <row r="378" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>11</v>
       </c>
@@ -24568,7 +24598,7 @@
       <c r="T378" s="2"/>
       <c r="U378" s="2"/>
     </row>
-    <row r="379" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>11</v>
       </c>
@@ -24618,7 +24648,7 @@
       <c r="T379" s="2"/>
       <c r="U379" s="2"/>
     </row>
-    <row r="380" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>11</v>
       </c>
@@ -24668,7 +24698,7 @@
       <c r="T380" s="2"/>
       <c r="U380" s="2"/>
     </row>
-    <row r="381" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>11</v>
       </c>
@@ -24718,7 +24748,7 @@
       <c r="T381" s="2"/>
       <c r="U381" s="2"/>
     </row>
-    <row r="382" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>11</v>
       </c>
@@ -24768,7 +24798,7 @@
       <c r="T382" s="2"/>
       <c r="U382" s="2"/>
     </row>
-    <row r="383" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>11</v>
       </c>
@@ -24818,7 +24848,7 @@
       <c r="T383" s="2"/>
       <c r="U383" s="2"/>
     </row>
-    <row r="384" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>11</v>
       </c>
@@ -24868,7 +24898,7 @@
       <c r="T384" s="2"/>
       <c r="U384" s="2"/>
     </row>
-    <row r="385" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>11</v>
       </c>
@@ -24918,7 +24948,7 @@
       <c r="T385" s="2"/>
       <c r="U385" s="2"/>
     </row>
-    <row r="386" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>11</v>
       </c>
@@ -24968,7 +24998,7 @@
       <c r="T386" s="2"/>
       <c r="U386" s="2"/>
     </row>
-    <row r="387" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>11</v>
       </c>
@@ -25018,7 +25048,7 @@
       <c r="T387" s="2"/>
       <c r="U387" s="2"/>
     </row>
-    <row r="388" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>11</v>
       </c>
@@ -25068,7 +25098,7 @@
       <c r="T388" s="2"/>
       <c r="U388" s="2"/>
     </row>
-    <row r="389" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>11</v>
       </c>
@@ -25118,7 +25148,7 @@
       <c r="T389" s="2"/>
       <c r="U389" s="2"/>
     </row>
-    <row r="390" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>11</v>
       </c>
@@ -25168,7 +25198,7 @@
       <c r="T390" s="2"/>
       <c r="U390" s="2"/>
     </row>
-    <row r="391" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>11</v>
       </c>
@@ -25218,7 +25248,7 @@
       <c r="T391" s="2"/>
       <c r="U391" s="2"/>
     </row>
-    <row r="392" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>11</v>
       </c>
@@ -25268,7 +25298,7 @@
       <c r="T392" s="2"/>
       <c r="U392" s="2"/>
     </row>
-    <row r="393" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>11</v>
       </c>
@@ -25318,7 +25348,7 @@
       <c r="T393" s="2"/>
       <c r="U393" s="2"/>
     </row>
-    <row r="394" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>11</v>
       </c>
@@ -25368,7 +25398,7 @@
       <c r="T394" s="2"/>
       <c r="U394" s="2"/>
     </row>
-    <row r="395" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>11</v>
       </c>
@@ -25418,7 +25448,7 @@
       <c r="T395" s="2"/>
       <c r="U395" s="2"/>
     </row>
-    <row r="396" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>11</v>
       </c>
@@ -25468,7 +25498,7 @@
       <c r="T396" s="2"/>
       <c r="U396" s="2"/>
     </row>
-    <row r="397" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>11</v>
       </c>
@@ -25518,7 +25548,7 @@
       <c r="T397" s="2"/>
       <c r="U397" s="2"/>
     </row>
-    <row r="398" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>11</v>
       </c>
@@ -25568,7 +25598,7 @@
       <c r="T398" s="2"/>
       <c r="U398" s="2"/>
     </row>
-    <row r="399" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>11</v>
       </c>
@@ -25618,7 +25648,7 @@
       <c r="T399" s="2"/>
       <c r="U399" s="2"/>
     </row>
-    <row r="400" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>11</v>
       </c>
@@ -25668,7 +25698,7 @@
       <c r="T400" s="2"/>
       <c r="U400" s="2"/>
     </row>
-    <row r="401" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>11</v>
       </c>
@@ -25718,7 +25748,7 @@
       <c r="T401" s="2"/>
       <c r="U401" s="2"/>
     </row>
-    <row r="402" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>11</v>
       </c>
@@ -25768,7 +25798,7 @@
       <c r="T402" s="2"/>
       <c r="U402" s="2"/>
     </row>
-    <row r="403" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>11</v>
       </c>
@@ -25818,7 +25848,7 @@
       <c r="T403" s="2"/>
       <c r="U403" s="2"/>
     </row>
-    <row r="404" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>11</v>
       </c>
@@ -25868,7 +25898,7 @@
       <c r="T404" s="2"/>
       <c r="U404" s="2"/>
     </row>
-    <row r="405" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>11</v>
       </c>
@@ -25918,7 +25948,7 @@
       <c r="T405" s="2"/>
       <c r="U405" s="2"/>
     </row>
-    <row r="406" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>11</v>
       </c>
@@ -25968,7 +25998,7 @@
       <c r="T406" s="2"/>
       <c r="U406" s="2"/>
     </row>
-    <row r="407" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>11</v>
       </c>
@@ -26018,7 +26048,7 @@
       <c r="T407" s="2"/>
       <c r="U407" s="2"/>
     </row>
-    <row r="408" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>11</v>
       </c>
@@ -26068,7 +26098,7 @@
       <c r="T408" s="2"/>
       <c r="U408" s="2"/>
     </row>
-    <row r="409" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>11</v>
       </c>
@@ -26118,7 +26148,7 @@
       <c r="T409" s="2"/>
       <c r="U409" s="2"/>
     </row>
-    <row r="410" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>11</v>
       </c>
@@ -26168,7 +26198,7 @@
       <c r="T410" s="2"/>
       <c r="U410" s="2"/>
     </row>
-    <row r="411" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>11</v>
       </c>
@@ -26218,7 +26248,7 @@
       <c r="T411" s="2"/>
       <c r="U411" s="2"/>
     </row>
-    <row r="412" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>11</v>
       </c>
@@ -26268,7 +26298,7 @@
       <c r="T412" s="2"/>
       <c r="U412" s="2"/>
     </row>
-    <row r="413" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>11</v>
       </c>
@@ -26318,7 +26348,7 @@
       <c r="T413" s="2"/>
       <c r="U413" s="2"/>
     </row>
-    <row r="414" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>11</v>
       </c>
@@ -26368,7 +26398,7 @@
       <c r="T414" s="2"/>
       <c r="U414" s="2"/>
     </row>
-    <row r="415" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>11</v>
       </c>
@@ -26418,7 +26448,7 @@
       <c r="T415" s="2"/>
       <c r="U415" s="2"/>
     </row>
-    <row r="416" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>11</v>
       </c>
@@ -26468,7 +26498,7 @@
       <c r="T416" s="2"/>
       <c r="U416" s="2"/>
     </row>
-    <row r="417" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>11</v>
       </c>
@@ -26518,7 +26548,7 @@
       <c r="T417" s="2"/>
       <c r="U417" s="2"/>
     </row>
-    <row r="418" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>11</v>
       </c>
@@ -26568,7 +26598,7 @@
       <c r="T418" s="2"/>
       <c r="U418" s="2"/>
     </row>
-    <row r="419" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>11</v>
       </c>
@@ -26618,7 +26648,7 @@
       <c r="T419" s="2"/>
       <c r="U419" s="2"/>
     </row>
-    <row r="420" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>11</v>
       </c>
@@ -26668,7 +26698,7 @@
       <c r="T420" s="2"/>
       <c r="U420" s="2"/>
     </row>
-    <row r="421" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>11</v>
       </c>
@@ -26718,7 +26748,7 @@
       <c r="T421" s="2"/>
       <c r="U421" s="2"/>
     </row>
-    <row r="422" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>11</v>
       </c>
@@ -26768,7 +26798,7 @@
       <c r="T422" s="2"/>
       <c r="U422" s="2"/>
     </row>
-    <row r="423" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>11</v>
       </c>
@@ -26818,7 +26848,7 @@
       <c r="T423" s="2"/>
       <c r="U423" s="2"/>
     </row>
-    <row r="424" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>11</v>
       </c>
@@ -26868,7 +26898,7 @@
       <c r="T424" s="2"/>
       <c r="U424" s="2"/>
     </row>
-    <row r="425" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>11</v>
       </c>
@@ -26918,7 +26948,7 @@
       <c r="T425" s="2"/>
       <c r="U425" s="2"/>
     </row>
-    <row r="426" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>11</v>
       </c>
@@ -26968,7 +26998,7 @@
       <c r="T426" s="2"/>
       <c r="U426" s="2"/>
     </row>
-    <row r="427" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>11</v>
       </c>
@@ -27018,7 +27048,7 @@
       <c r="T427" s="2"/>
       <c r="U427" s="2"/>
     </row>
-    <row r="428" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>11</v>
       </c>
@@ -27068,7 +27098,7 @@
       <c r="T428" s="2"/>
       <c r="U428" s="2"/>
     </row>
-    <row r="429" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>11</v>
       </c>
@@ -27118,7 +27148,7 @@
       <c r="T429" s="2"/>
       <c r="U429" s="2"/>
     </row>
-    <row r="430" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>11</v>
       </c>
@@ -27168,7 +27198,7 @@
       <c r="T430" s="2"/>
       <c r="U430" s="2"/>
     </row>
-    <row r="431" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>11</v>
       </c>
@@ -27218,7 +27248,7 @@
       <c r="T431" s="2"/>
       <c r="U431" s="2"/>
     </row>
-    <row r="432" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>11</v>
       </c>
@@ -27268,7 +27298,7 @@
       <c r="T432" s="2"/>
       <c r="U432" s="2"/>
     </row>
-    <row r="433" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>11</v>
       </c>
@@ -27318,7 +27348,7 @@
       <c r="T433" s="2"/>
       <c r="U433" s="2"/>
     </row>
-    <row r="434" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>11</v>
       </c>
@@ -27368,7 +27398,7 @@
       <c r="T434" s="2"/>
       <c r="U434" s="2"/>
     </row>
-    <row r="435" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>11</v>
       </c>
@@ -27418,7 +27448,7 @@
       <c r="T435" s="2"/>
       <c r="U435" s="2"/>
     </row>
-    <row r="436" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>11</v>
       </c>
@@ -27468,7 +27498,7 @@
       <c r="T436" s="2"/>
       <c r="U436" s="2"/>
     </row>
-    <row r="437" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>11</v>
       </c>
@@ -27518,7 +27548,7 @@
       <c r="T437" s="2"/>
       <c r="U437" s="2"/>
     </row>
-    <row r="438" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>11</v>
       </c>
@@ -27568,7 +27598,7 @@
       <c r="T438" s="2"/>
       <c r="U438" s="2"/>
     </row>
-    <row r="439" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>11</v>
       </c>
@@ -27618,7 +27648,7 @@
       <c r="T439" s="2"/>
       <c r="U439" s="2"/>
     </row>
-    <row r="440" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>11</v>
       </c>
@@ -27668,7 +27698,7 @@
       <c r="T440" s="2"/>
       <c r="U440" s="2"/>
     </row>
-    <row r="441" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>11</v>
       </c>
@@ -27718,7 +27748,7 @@
       <c r="T441" s="2"/>
       <c r="U441" s="2"/>
     </row>
-    <row r="442" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>11</v>
       </c>
@@ -27768,7 +27798,7 @@
       <c r="T442" s="2"/>
       <c r="U442" s="2"/>
     </row>
-    <row r="443" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>11</v>
       </c>
@@ -27818,7 +27848,7 @@
       <c r="T443" s="2"/>
       <c r="U443" s="2"/>
     </row>
-    <row r="444" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>11</v>
       </c>
@@ -27868,7 +27898,7 @@
       <c r="T444" s="2"/>
       <c r="U444" s="2"/>
     </row>
-    <row r="445" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>11</v>
       </c>
@@ -27918,7 +27948,7 @@
       <c r="T445" s="2"/>
       <c r="U445" s="2"/>
     </row>
-    <row r="446" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>11</v>
       </c>
@@ -27968,7 +27998,7 @@
       <c r="T446" s="2"/>
       <c r="U446" s="2"/>
     </row>
-    <row r="447" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>11</v>
       </c>
@@ -28018,7 +28048,7 @@
       <c r="T447" s="2"/>
       <c r="U447" s="2"/>
     </row>
-    <row r="448" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>11</v>
       </c>
@@ -28068,7 +28098,7 @@
       <c r="T448" s="2"/>
       <c r="U448" s="2"/>
     </row>
-    <row r="449" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>11</v>
       </c>
@@ -28118,7 +28148,7 @@
       <c r="T449" s="2"/>
       <c r="U449" s="2"/>
     </row>
-    <row r="450" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>11</v>
       </c>
@@ -28168,7 +28198,7 @@
       <c r="T450" s="2"/>
       <c r="U450" s="2"/>
     </row>
-    <row r="451" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>11</v>
       </c>
@@ -28218,7 +28248,7 @@
       <c r="T451" s="2"/>
       <c r="U451" s="2"/>
     </row>
-    <row r="452" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>11</v>
       </c>
@@ -28268,7 +28298,7 @@
       <c r="T452" s="2"/>
       <c r="U452" s="2"/>
     </row>
-    <row r="453" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>11</v>
       </c>
@@ -28318,7 +28348,7 @@
       <c r="T453" s="2"/>
       <c r="U453" s="2"/>
     </row>
-    <row r="454" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>11</v>
       </c>
@@ -28368,7 +28398,7 @@
       <c r="T454" s="2"/>
       <c r="U454" s="2"/>
     </row>
-    <row r="455" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>11</v>
       </c>
@@ -28418,7 +28448,7 @@
       <c r="T455" s="2"/>
       <c r="U455" s="2"/>
     </row>
-    <row r="456" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>11</v>
       </c>
@@ -28468,7 +28498,7 @@
       <c r="T456" s="2"/>
       <c r="U456" s="2"/>
     </row>
-    <row r="457" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>11</v>
       </c>
@@ -28518,7 +28548,7 @@
       <c r="T457" s="2"/>
       <c r="U457" s="2"/>
     </row>
-    <row r="458" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>11</v>
       </c>
@@ -28568,7 +28598,7 @@
       <c r="T458" s="2"/>
       <c r="U458" s="2"/>
     </row>
-    <row r="459" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>11</v>
       </c>
@@ -28618,7 +28648,7 @@
       <c r="T459" s="2"/>
       <c r="U459" s="2"/>
     </row>
-    <row r="460" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>11</v>
       </c>
@@ -28668,7 +28698,7 @@
       <c r="T460" s="2"/>
       <c r="U460" s="2"/>
     </row>
-    <row r="461" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>11</v>
       </c>
@@ -28718,7 +28748,7 @@
       <c r="T461" s="2"/>
       <c r="U461" s="2"/>
     </row>
-    <row r="462" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>11</v>
       </c>
@@ -28768,7 +28798,7 @@
       <c r="T462" s="2"/>
       <c r="U462" s="2"/>
     </row>
-    <row r="463" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>11</v>
       </c>
@@ -28818,7 +28848,7 @@
       <c r="T463" s="2"/>
       <c r="U463" s="2"/>
     </row>
-    <row r="464" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>11</v>
       </c>
@@ -28868,7 +28898,7 @@
       <c r="T464" s="2"/>
       <c r="U464" s="2"/>
     </row>
-    <row r="465" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>11</v>
       </c>
@@ -28918,7 +28948,7 @@
       <c r="T465" s="2"/>
       <c r="U465" s="2"/>
     </row>
-    <row r="466" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>11</v>
       </c>
@@ -28968,7 +28998,7 @@
       <c r="T466" s="2"/>
       <c r="U466" s="2"/>
     </row>
-    <row r="467" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>11</v>
       </c>
@@ -29018,7 +29048,7 @@
       <c r="T467" s="2"/>
       <c r="U467" s="2"/>
     </row>
-    <row r="468" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>11</v>
       </c>
@@ -29068,7 +29098,7 @@
       <c r="T468" s="2"/>
       <c r="U468" s="2"/>
     </row>
-    <row r="469" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>11</v>
       </c>
@@ -29118,7 +29148,7 @@
       <c r="T469" s="2"/>
       <c r="U469" s="2"/>
     </row>
-    <row r="470" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>11</v>
       </c>
@@ -29168,7 +29198,7 @@
       <c r="T470" s="2"/>
       <c r="U470" s="2"/>
     </row>
-    <row r="471" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>11</v>
       </c>
@@ -29218,7 +29248,7 @@
       <c r="T471" s="2"/>
       <c r="U471" s="2"/>
     </row>
-    <row r="472" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>11</v>
       </c>
@@ -29268,7 +29298,7 @@
       <c r="T472" s="2"/>
       <c r="U472" s="2"/>
     </row>
-    <row r="473" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>11</v>
       </c>
@@ -29318,7 +29348,7 @@
       <c r="T473" s="2"/>
       <c r="U473" s="2"/>
     </row>
-    <row r="474" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>11</v>
       </c>
@@ -29368,7 +29398,7 @@
       <c r="T474" s="2"/>
       <c r="U474" s="2"/>
     </row>
-    <row r="475" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>11</v>
       </c>
@@ -29418,7 +29448,7 @@
       <c r="T475" s="2"/>
       <c r="U475" s="2"/>
     </row>
-    <row r="476" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>11</v>
       </c>
@@ -29468,7 +29498,7 @@
       <c r="T476" s="2"/>
       <c r="U476" s="2"/>
     </row>
-    <row r="477" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>11</v>
       </c>
@@ -29518,7 +29548,7 @@
       <c r="T477" s="2"/>
       <c r="U477" s="2"/>
     </row>
-    <row r="478" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>11</v>
       </c>
@@ -29568,7 +29598,7 @@
       <c r="T478" s="2"/>
       <c r="U478" s="2"/>
     </row>
-    <row r="479" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>11</v>
       </c>
@@ -29618,7 +29648,7 @@
       <c r="T479" s="2"/>
       <c r="U479" s="2"/>
     </row>
-    <row r="480" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>11</v>
       </c>
@@ -29668,7 +29698,7 @@
       <c r="T480" s="2"/>
       <c r="U480" s="2"/>
     </row>
-    <row r="481" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>11</v>
       </c>
@@ -29718,7 +29748,7 @@
       <c r="T481" s="2"/>
       <c r="U481" s="2"/>
     </row>
-    <row r="482" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>11</v>
       </c>
@@ -29768,7 +29798,7 @@
       <c r="T482" s="2"/>
       <c r="U482" s="2"/>
     </row>
-    <row r="483" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>11</v>
       </c>
@@ -29818,7 +29848,7 @@
       <c r="T483" s="2"/>
       <c r="U483" s="2"/>
     </row>
-    <row r="484" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>11</v>
       </c>
@@ -29868,7 +29898,7 @@
       <c r="T484" s="2"/>
       <c r="U484" s="2"/>
     </row>
-    <row r="485" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>11</v>
       </c>
@@ -29918,7 +29948,7 @@
       <c r="T485" s="2"/>
       <c r="U485" s="2"/>
     </row>
-    <row r="486" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>11</v>
       </c>
@@ -29968,7 +29998,7 @@
       <c r="T486" s="2"/>
       <c r="U486" s="2"/>
     </row>
-    <row r="487" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>11</v>
       </c>
@@ -30018,7 +30048,7 @@
       <c r="T487" s="2"/>
       <c r="U487" s="2"/>
     </row>
-    <row r="488" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>11</v>
       </c>
@@ -30068,7 +30098,7 @@
       <c r="T488" s="2"/>
       <c r="U488" s="2"/>
     </row>
-    <row r="489" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>11</v>
       </c>
@@ -30118,7 +30148,7 @@
       <c r="T489" s="2"/>
       <c r="U489" s="2"/>
     </row>
-    <row r="490" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>11</v>
       </c>
@@ -30168,7 +30198,7 @@
       <c r="T490" s="2"/>
       <c r="U490" s="2"/>
     </row>
-    <row r="491" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>11</v>
       </c>
@@ -30218,7 +30248,7 @@
       <c r="T491" s="2"/>
       <c r="U491" s="2"/>
     </row>
-    <row r="492" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>11</v>
       </c>
@@ -30268,7 +30298,7 @@
       <c r="T492" s="2"/>
       <c r="U492" s="2"/>
     </row>
-    <row r="493" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>11</v>
       </c>
@@ -30318,7 +30348,7 @@
       <c r="T493" s="2"/>
       <c r="U493" s="2"/>
     </row>
-    <row r="494" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>11</v>
       </c>
@@ -30368,7 +30398,7 @@
       <c r="T494" s="2"/>
       <c r="U494" s="2"/>
     </row>
-    <row r="495" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>11</v>
       </c>
@@ -30418,7 +30448,7 @@
       <c r="T495" s="2"/>
       <c r="U495" s="2"/>
     </row>
-    <row r="496" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>11</v>
       </c>
@@ -30468,7 +30498,7 @@
       <c r="T496" s="2"/>
       <c r="U496" s="2"/>
     </row>
-    <row r="497" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>11</v>
       </c>
@@ -30518,7 +30548,7 @@
       <c r="T497" s="2"/>
       <c r="U497" s="2"/>
     </row>
-    <row r="498" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>11</v>
       </c>
@@ -30568,7 +30598,7 @@
       <c r="T498" s="2"/>
       <c r="U498" s="2"/>
     </row>
-    <row r="499" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>11</v>
       </c>
@@ -30618,7 +30648,7 @@
       <c r="T499" s="2"/>
       <c r="U499" s="2"/>
     </row>
-    <row r="500" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>11</v>
       </c>
@@ -30668,7 +30698,7 @@
       <c r="T500" s="2"/>
       <c r="U500" s="2"/>
     </row>
-    <row r="501" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>11</v>
       </c>
@@ -30718,7 +30748,7 @@
       <c r="T501" s="2"/>
       <c r="U501" s="2"/>
     </row>
-    <row r="502" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>11</v>
       </c>
@@ -30768,7 +30798,7 @@
       <c r="T502" s="2"/>
       <c r="U502" s="2"/>
     </row>
-    <row r="503" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>11</v>
       </c>
@@ -30818,7 +30848,7 @@
       <c r="T503" s="2"/>
       <c r="U503" s="2"/>
     </row>
-    <row r="504" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>11</v>
       </c>
@@ -30868,7 +30898,7 @@
       <c r="T504" s="2"/>
       <c r="U504" s="2"/>
     </row>
-    <row r="505" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>11</v>
       </c>
@@ -30918,7 +30948,7 @@
       <c r="T505" s="2"/>
       <c r="U505" s="2"/>
     </row>
-    <row r="506" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>11</v>
       </c>
@@ -30968,7 +30998,7 @@
       <c r="T506" s="2"/>
       <c r="U506" s="2"/>
     </row>
-    <row r="507" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>11</v>
       </c>
@@ -31018,7 +31048,7 @@
       <c r="T507" s="2"/>
       <c r="U507" s="2"/>
     </row>
-    <row r="508" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>11</v>
       </c>
@@ -31068,7 +31098,7 @@
       <c r="T508" s="2"/>
       <c r="U508" s="2"/>
     </row>
-    <row r="509" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>11</v>
       </c>
@@ -31118,7 +31148,7 @@
       <c r="T509" s="2"/>
       <c r="U509" s="2"/>
     </row>
-    <row r="510" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>11</v>
       </c>
@@ -31574,7 +31604,7 @@
       <c r="T517" s="2"/>
       <c r="U517" s="2"/>
     </row>
-    <row r="518" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>11</v>
       </c>
@@ -31856,7 +31886,7 @@
       <c r="T522" s="2"/>
       <c r="U522" s="2"/>
     </row>
-    <row r="523" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>11</v>
       </c>
@@ -31964,7 +31994,7 @@
       <c r="T524" s="2"/>
       <c r="U524" s="2"/>
     </row>
-    <row r="525" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>11</v>
       </c>
@@ -32188,7 +32218,7 @@
       <c r="T528" s="2"/>
       <c r="U528" s="2"/>
     </row>
-    <row r="529" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>11</v>
       </c>
@@ -32238,7 +32268,7 @@
       <c r="T529" s="2"/>
       <c r="U529" s="2"/>
     </row>
-    <row r="530" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>11</v>
       </c>
@@ -32288,7 +32318,7 @@
       <c r="T530" s="2"/>
       <c r="U530" s="2"/>
     </row>
-    <row r="531" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>11</v>
       </c>
@@ -32338,7 +32368,7 @@
       <c r="T531" s="2"/>
       <c r="U531" s="2"/>
     </row>
-    <row r="532" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>11</v>
       </c>
@@ -32356,7 +32386,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G532" s="2"/>
+      <c r="G532" s="9">
+        <v>46230</v>
+      </c>
       <c r="H532" s="2"/>
       <c r="I532" s="2"/>
       <c r="J532" s="2"/>
@@ -32364,7 +32396,7 @@
         <v>728</v>
       </c>
       <c r="L532" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M532" s="2" t="s">
         <v>16</v>
@@ -32388,7 +32420,7 @@
       <c r="T532" s="2"/>
       <c r="U532" s="2"/>
     </row>
-    <row r="533" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>11</v>
       </c>
@@ -32438,7 +32470,7 @@
       <c r="T533" s="2"/>
       <c r="U533" s="2"/>
     </row>
-    <row r="534" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>11</v>
       </c>
@@ -32488,7 +32520,7 @@
       <c r="T534" s="2"/>
       <c r="U534" s="2"/>
     </row>
-    <row r="535" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>11</v>
       </c>
@@ -32538,7 +32570,7 @@
       <c r="T535" s="2"/>
       <c r="U535" s="2"/>
     </row>
-    <row r="536" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>11</v>
       </c>
@@ -32588,7 +32620,7 @@
       <c r="T536" s="2"/>
       <c r="U536" s="2"/>
     </row>
-    <row r="537" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>11</v>
       </c>
@@ -32638,7 +32670,7 @@
       <c r="T537" s="2"/>
       <c r="U537" s="2"/>
     </row>
-    <row r="538" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>11</v>
       </c>
@@ -32688,7 +32720,7 @@
       <c r="T538" s="2"/>
       <c r="U538" s="2"/>
     </row>
-    <row r="539" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>11</v>
       </c>
@@ -32738,7 +32770,7 @@
       <c r="T539" s="2"/>
       <c r="U539" s="2"/>
     </row>
-    <row r="540" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>11</v>
       </c>
@@ -32788,7 +32820,7 @@
       <c r="T540" s="2"/>
       <c r="U540" s="2"/>
     </row>
-    <row r="541" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>11</v>
       </c>
@@ -32838,7 +32870,7 @@
       <c r="T541" s="2"/>
       <c r="U541" s="2"/>
     </row>
-    <row r="542" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>11</v>
       </c>
@@ -32888,7 +32920,7 @@
       <c r="T542" s="2"/>
       <c r="U542" s="2"/>
     </row>
-    <row r="543" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>11</v>
       </c>
@@ -32938,7 +32970,7 @@
       <c r="T543" s="2"/>
       <c r="U543" s="2"/>
     </row>
-    <row r="544" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>11</v>
       </c>
@@ -32988,7 +33020,7 @@
       <c r="T544" s="2"/>
       <c r="U544" s="2"/>
     </row>
-    <row r="545" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>11</v>
       </c>
@@ -33038,7 +33070,7 @@
       <c r="T545" s="2"/>
       <c r="U545" s="2"/>
     </row>
-    <row r="546" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>11</v>
       </c>
@@ -33088,7 +33120,7 @@
       <c r="T546" s="2"/>
       <c r="U546" s="2"/>
     </row>
-    <row r="547" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>11</v>
       </c>
@@ -33196,7 +33228,7 @@
       <c r="T548" s="2"/>
       <c r="U548" s="2"/>
     </row>
-    <row r="549" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>11</v>
       </c>
@@ -33304,7 +33336,7 @@
       <c r="T550" s="2"/>
       <c r="U550" s="2"/>
     </row>
-    <row r="551" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>11</v>
       </c>
@@ -33412,7 +33444,7 @@
       <c r="T552" s="2"/>
       <c r="U552" s="2"/>
     </row>
-    <row r="553" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>11</v>
       </c>
@@ -33462,7 +33494,7 @@
       <c r="T553" s="2"/>
       <c r="U553" s="2"/>
     </row>
-    <row r="554" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>11</v>
       </c>
@@ -33512,7 +33544,7 @@
       <c r="T554" s="2"/>
       <c r="U554" s="2"/>
     </row>
-    <row r="555" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>11</v>
       </c>
@@ -33562,7 +33594,7 @@
       <c r="T555" s="2"/>
       <c r="U555" s="2"/>
     </row>
-    <row r="556" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>11</v>
       </c>
@@ -33612,7 +33644,7 @@
       <c r="T556" s="2"/>
       <c r="U556" s="2"/>
     </row>
-    <row r="557" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>11</v>
       </c>
@@ -34010,7 +34042,7 @@
       <c r="T563" s="2"/>
       <c r="U563" s="2"/>
     </row>
-    <row r="564" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>11</v>
       </c>
@@ -34028,7 +34060,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G564" s="2"/>
+      <c r="G564" s="9">
+        <v>46230</v>
+      </c>
       <c r="H564" s="2"/>
       <c r="I564" s="2"/>
       <c r="J564" s="2"/>
@@ -34036,7 +34070,7 @@
         <v>13</v>
       </c>
       <c r="L564" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M564" s="2" t="s">
         <v>16</v>
@@ -34060,7 +34094,7 @@
       <c r="T564" s="2"/>
       <c r="U564" s="2"/>
     </row>
-    <row r="565" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>11</v>
       </c>
@@ -34078,7 +34112,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G565" s="2"/>
+      <c r="G565" s="9">
+        <v>46230</v>
+      </c>
       <c r="H565" s="2"/>
       <c r="I565" s="2"/>
       <c r="J565" s="2"/>
@@ -34086,7 +34122,7 @@
         <v>13</v>
       </c>
       <c r="L565" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M565" s="2" t="s">
         <v>16</v>
@@ -34110,7 +34146,7 @@
       <c r="T565" s="2"/>
       <c r="U565" s="2"/>
     </row>
-    <row r="566" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>11</v>
       </c>
@@ -34160,7 +34196,7 @@
       <c r="T566" s="2"/>
       <c r="U566" s="2"/>
     </row>
-    <row r="567" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>11</v>
       </c>
@@ -34210,7 +34246,7 @@
       <c r="T567" s="2"/>
       <c r="U567" s="2"/>
     </row>
-    <row r="568" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>11</v>
       </c>
@@ -34318,7 +34354,7 @@
       <c r="T569" s="2"/>
       <c r="U569" s="2"/>
     </row>
-    <row r="570" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>11</v>
       </c>
@@ -34368,7 +34404,7 @@
       <c r="T570" s="2"/>
       <c r="U570" s="2"/>
     </row>
-    <row r="571" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>11</v>
       </c>
@@ -34418,7 +34454,7 @@
       <c r="T571" s="2"/>
       <c r="U571" s="2"/>
     </row>
-    <row r="572" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>11</v>
       </c>
@@ -34584,7 +34620,7 @@
       <c r="T574" s="2"/>
       <c r="U574" s="2"/>
     </row>
-    <row r="575" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>11</v>
       </c>
@@ -34634,7 +34670,7 @@
       <c r="T575" s="2"/>
       <c r="U575" s="2"/>
     </row>
-    <row r="576" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>11</v>
       </c>
@@ -34684,7 +34720,7 @@
       <c r="T576" s="2"/>
       <c r="U576" s="2"/>
     </row>
-    <row r="577" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>11</v>
       </c>
@@ -34734,7 +34770,7 @@
       <c r="T577" s="2"/>
       <c r="U577" s="2"/>
     </row>
-    <row r="578" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>11</v>
       </c>
@@ -34784,7 +34820,7 @@
       <c r="T578" s="2"/>
       <c r="U578" s="2"/>
     </row>
-    <row r="579" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>11</v>
       </c>
@@ -34834,7 +34870,7 @@
       <c r="T579" s="2"/>
       <c r="U579" s="2"/>
     </row>
-    <row r="580" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>11</v>
       </c>
@@ -34884,7 +34920,7 @@
       <c r="T580" s="2"/>
       <c r="U580" s="2"/>
     </row>
-    <row r="581" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>11</v>
       </c>
@@ -34934,7 +34970,7 @@
       <c r="T581" s="2"/>
       <c r="U581" s="2"/>
     </row>
-    <row r="582" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>11</v>
       </c>
@@ -34984,7 +35020,7 @@
       <c r="T582" s="2"/>
       <c r="U582" s="2"/>
     </row>
-    <row r="583" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>11</v>
       </c>
@@ -35034,7 +35070,7 @@
       <c r="T583" s="2"/>
       <c r="U583" s="2"/>
     </row>
-    <row r="584" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>11</v>
       </c>
@@ -35084,7 +35120,7 @@
       <c r="T584" s="2"/>
       <c r="U584" s="2"/>
     </row>
-    <row r="585" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>11</v>
       </c>
@@ -35308,7 +35344,7 @@
       <c r="T588" s="2"/>
       <c r="U588" s="2"/>
     </row>
-    <row r="589" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>11</v>
       </c>
@@ -35326,7 +35362,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G589" s="2"/>
+      <c r="G589" s="9">
+        <v>46230</v>
+      </c>
       <c r="H589" s="2"/>
       <c r="I589" s="2"/>
       <c r="J589" s="2"/>
@@ -35334,10 +35372,10 @@
         <v>13</v>
       </c>
       <c r="L589" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M589" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N589" s="2" t="s">
         <v>75</v>
@@ -35416,7 +35454,7 @@
       <c r="T590" s="2"/>
       <c r="U590" s="2"/>
     </row>
-    <row r="591" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>11</v>
       </c>
@@ -35466,7 +35504,7 @@
       <c r="T591" s="2"/>
       <c r="U591" s="2"/>
     </row>
-    <row r="592" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>11</v>
       </c>
@@ -35806,7 +35844,7 @@
       <c r="T597" s="2"/>
       <c r="U597" s="2"/>
     </row>
-    <row r="598" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>11</v>
       </c>
@@ -36146,7 +36184,7 @@
       <c r="T603" s="2"/>
       <c r="U603" s="2"/>
     </row>
-    <row r="604" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>11</v>
       </c>
@@ -36254,7 +36292,7 @@
       <c r="T605" s="2"/>
       <c r="U605" s="2"/>
     </row>
-    <row r="606" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>11</v>
       </c>
@@ -36594,7 +36632,7 @@
       <c r="T611" s="2"/>
       <c r="U611" s="2"/>
     </row>
-    <row r="612" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>11</v>
       </c>
@@ -36702,7 +36740,7 @@
       <c r="T613" s="2"/>
       <c r="U613" s="2"/>
     </row>
-    <row r="614" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>11</v>
       </c>
@@ -36810,7 +36848,7 @@
       <c r="T615" s="2"/>
       <c r="U615" s="2"/>
     </row>
-    <row r="616" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>11</v>
       </c>
@@ -37034,7 +37072,7 @@
       <c r="T619" s="2"/>
       <c r="U619" s="2"/>
     </row>
-    <row r="620" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>11</v>
       </c>
@@ -37200,7 +37238,7 @@
       <c r="T622" s="2"/>
       <c r="U622" s="2"/>
     </row>
-    <row r="623" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>11</v>
       </c>
@@ -37250,7 +37288,7 @@
       <c r="T623" s="2"/>
       <c r="U623" s="2"/>
     </row>
-    <row r="624" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>11</v>
       </c>
@@ -37648,7 +37686,7 @@
       <c r="T630" s="2"/>
       <c r="U630" s="2"/>
     </row>
-    <row r="631" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>11</v>
       </c>
@@ -38162,7 +38200,7 @@
       <c r="T639" s="2"/>
       <c r="U639" s="2"/>
     </row>
-    <row r="640" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>11</v>
       </c>
@@ -38212,7 +38250,7 @@
       <c r="T640" s="2"/>
       <c r="U640" s="2"/>
     </row>
-    <row r="641" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>11</v>
       </c>
@@ -38262,7 +38300,7 @@
       <c r="T641" s="2"/>
       <c r="U641" s="2"/>
     </row>
-    <row r="642" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>11</v>
       </c>
@@ -38312,7 +38350,7 @@
       <c r="T642" s="2"/>
       <c r="U642" s="2"/>
     </row>
-    <row r="643" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>11</v>
       </c>
@@ -38362,7 +38400,7 @@
       <c r="T643" s="2"/>
       <c r="U643" s="2"/>
     </row>
-    <row r="644" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>11</v>
       </c>
@@ -38528,7 +38566,7 @@
       <c r="T646" s="2"/>
       <c r="U646" s="2"/>
     </row>
-    <row r="647" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>11</v>
       </c>
@@ -38578,7 +38616,7 @@
       <c r="T647" s="2"/>
       <c r="U647" s="2"/>
     </row>
-    <row r="648" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>11</v>
       </c>
@@ -38628,7 +38666,7 @@
       <c r="T648" s="2"/>
       <c r="U648" s="2"/>
     </row>
-    <row r="649" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>11</v>
       </c>
@@ -38678,7 +38716,7 @@
       <c r="T649" s="2"/>
       <c r="U649" s="2"/>
     </row>
-    <row r="650" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>11</v>
       </c>
@@ -38786,7 +38824,7 @@
       <c r="T651" s="2"/>
       <c r="U651" s="2"/>
     </row>
-    <row r="652" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>11</v>
       </c>
@@ -38836,7 +38874,7 @@
       <c r="T652" s="2"/>
       <c r="U652" s="2"/>
     </row>
-    <row r="653" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>11</v>
       </c>
@@ -38886,7 +38924,7 @@
       <c r="T653" s="2"/>
       <c r="U653" s="2"/>
     </row>
-    <row r="654" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>11</v>
       </c>
@@ -38936,7 +38974,7 @@
       <c r="T654" s="2"/>
       <c r="U654" s="2"/>
     </row>
-    <row r="655" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>11</v>
       </c>
@@ -38986,7 +39024,7 @@
       <c r="T655" s="2"/>
       <c r="U655" s="2"/>
     </row>
-    <row r="656" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>11</v>
       </c>
@@ -39036,7 +39074,7 @@
       <c r="T656" s="2"/>
       <c r="U656" s="2"/>
     </row>
-    <row r="657" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>11</v>
       </c>
@@ -39086,7 +39124,7 @@
       <c r="T657" s="2"/>
       <c r="U657" s="2"/>
     </row>
-    <row r="658" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>11</v>
       </c>
@@ -39136,7 +39174,7 @@
       <c r="T658" s="2"/>
       <c r="U658" s="2"/>
     </row>
-    <row r="659" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>11</v>
       </c>
@@ -39186,7 +39224,7 @@
       <c r="T659" s="2"/>
       <c r="U659" s="2"/>
     </row>
-    <row r="660" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>11</v>
       </c>
@@ -39294,7 +39332,7 @@
       <c r="T661" s="2"/>
       <c r="U661" s="2"/>
     </row>
-    <row r="662" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>11</v>
       </c>
@@ -39344,7 +39382,7 @@
       <c r="T662" s="2"/>
       <c r="U662" s="2"/>
     </row>
-    <row r="663" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>11</v>
       </c>
@@ -39626,7 +39664,7 @@
       <c r="T667" s="2"/>
       <c r="U667" s="2"/>
     </row>
-    <row r="668" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>11</v>
       </c>
@@ -39676,7 +39714,7 @@
       <c r="T668" s="2"/>
       <c r="U668" s="2"/>
     </row>
-    <row r="669" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>11</v>
       </c>
@@ -39726,7 +39764,7 @@
       <c r="T669" s="2"/>
       <c r="U669" s="2"/>
     </row>
-    <row r="670" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>11</v>
       </c>
@@ -39776,7 +39814,7 @@
       <c r="T670" s="2"/>
       <c r="U670" s="2"/>
     </row>
-    <row r="671" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>11</v>
       </c>
@@ -39826,7 +39864,7 @@
       <c r="T671" s="2"/>
       <c r="U671" s="2"/>
     </row>
-    <row r="672" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>11</v>
       </c>
@@ -39876,7 +39914,7 @@
       <c r="T672" s="2"/>
       <c r="U672" s="2"/>
     </row>
-    <row r="673" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>11</v>
       </c>
@@ -40042,7 +40080,7 @@
       <c r="T675" s="2"/>
       <c r="U675" s="2"/>
     </row>
-    <row r="676" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>11</v>
       </c>
@@ -40068,7 +40106,7 @@
         <v>74</v>
       </c>
       <c r="L676" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M676" s="2" t="s">
         <v>16</v>
@@ -40092,7 +40130,7 @@
       <c r="T676" s="2"/>
       <c r="U676" s="2"/>
     </row>
-    <row r="677" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>11</v>
       </c>
@@ -40118,7 +40156,7 @@
         <v>78</v>
       </c>
       <c r="L677" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M677" s="2" t="s">
         <v>16</v>
@@ -40142,7 +40180,7 @@
       <c r="T677" s="2"/>
       <c r="U677" s="2"/>
     </row>
-    <row r="678" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>11</v>
       </c>
@@ -40168,7 +40206,7 @@
         <v>81</v>
       </c>
       <c r="L678" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M678" s="2" t="s">
         <v>16</v>
@@ -40192,7 +40230,7 @@
       <c r="T678" s="2"/>
       <c r="U678" s="2"/>
     </row>
-    <row r="679" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>11</v>
       </c>
@@ -40242,7 +40280,7 @@
       <c r="T679" s="2"/>
       <c r="U679" s="2"/>
     </row>
-    <row r="680" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>11</v>
       </c>
@@ -40260,7 +40298,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G680" s="2"/>
+      <c r="G680" s="9">
+        <v>46230</v>
+      </c>
       <c r="H680" s="2"/>
       <c r="I680" s="2"/>
       <c r="J680" s="2"/>
@@ -40268,7 +40308,7 @@
         <v>721</v>
       </c>
       <c r="L680" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M680" s="2" t="s">
         <v>16</v>
@@ -40292,7 +40332,7 @@
       <c r="T680" s="2"/>
       <c r="U680" s="2"/>
     </row>
-    <row r="681" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>11</v>
       </c>
@@ -40310,7 +40350,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G681" s="2"/>
+      <c r="G681" s="9">
+        <v>46230</v>
+      </c>
       <c r="H681" s="2"/>
       <c r="I681" s="2"/>
       <c r="J681" s="2"/>
@@ -40318,7 +40360,7 @@
         <v>723</v>
       </c>
       <c r="L681" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M681" s="2" t="s">
         <v>16</v>
@@ -40342,7 +40384,7 @@
       <c r="T681" s="2"/>
       <c r="U681" s="2"/>
     </row>
-    <row r="682" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>11</v>
       </c>
@@ -40360,7 +40402,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G682" s="2"/>
+      <c r="G682" s="9">
+        <v>46230</v>
+      </c>
       <c r="H682" s="2"/>
       <c r="I682" s="2"/>
       <c r="J682" s="2"/>
@@ -40368,7 +40412,7 @@
         <v>725</v>
       </c>
       <c r="L682" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M682" s="2" t="s">
         <v>16</v>
@@ -40392,7 +40436,7 @@
       <c r="T682" s="2"/>
       <c r="U682" s="2"/>
     </row>
-    <row r="683" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>11</v>
       </c>
@@ -40442,7 +40486,7 @@
       <c r="T683" s="2"/>
       <c r="U683" s="2"/>
     </row>
-    <row r="684" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>11</v>
       </c>
@@ -40468,7 +40512,7 @@
         <v>908</v>
       </c>
       <c r="L684" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M684" s="2" t="s">
         <v>16</v>
@@ -40492,7 +40536,7 @@
       <c r="T684" s="2"/>
       <c r="U684" s="2"/>
     </row>
-    <row r="685" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>11</v>
       </c>
@@ -40510,7 +40554,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G685" s="2"/>
+      <c r="G685" s="9">
+        <v>46230</v>
+      </c>
       <c r="H685" s="2"/>
       <c r="I685" s="2"/>
       <c r="J685" s="2"/>
@@ -40518,7 +40564,7 @@
         <v>13</v>
       </c>
       <c r="L685" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M685" s="2" t="s">
         <v>16</v>
@@ -40542,7 +40588,7 @@
       <c r="T685" s="2"/>
       <c r="U685" s="2"/>
     </row>
-    <row r="686" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>11</v>
       </c>
@@ -40592,7 +40638,7 @@
       <c r="T686" s="2"/>
       <c r="U686" s="2"/>
     </row>
-    <row r="687" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>11</v>
       </c>
@@ -40618,7 +40664,7 @@
         <v>1036</v>
       </c>
       <c r="L687" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M687" s="2" t="s">
         <v>16</v>
@@ -40642,7 +40688,7 @@
       <c r="T687" s="2"/>
       <c r="U687" s="2"/>
     </row>
-    <row r="688" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>11</v>
       </c>
@@ -40668,7 +40714,7 @@
         <v>13</v>
       </c>
       <c r="L688" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M688" s="2" t="s">
         <v>16</v>
@@ -40692,7 +40738,7 @@
       <c r="T688" s="2"/>
       <c r="U688" s="2"/>
     </row>
-    <row r="689" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>11</v>
       </c>
@@ -40710,7 +40756,9 @@
         <f>VLOOKUP(C:C,Vlookup!A:A,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="G689" s="2"/>
+      <c r="G689" s="9">
+        <v>46230</v>
+      </c>
       <c r="H689" s="2"/>
       <c r="I689" s="2"/>
       <c r="J689" s="2"/>
@@ -40718,7 +40766,7 @@
         <v>1133</v>
       </c>
       <c r="L689" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M689" s="2" t="s">
         <v>16</v>
@@ -40742,7 +40790,7 @@
       <c r="T689" s="2"/>
       <c r="U689" s="2"/>
     </row>
-    <row r="690" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>11</v>
       </c>
@@ -40768,7 +40816,7 @@
         <v>13</v>
       </c>
       <c r="L690" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M690" s="2" t="s">
         <v>16</v>
@@ -40792,7 +40840,7 @@
       <c r="T690" s="2"/>
       <c r="U690" s="2"/>
     </row>
-    <row r="691" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>11</v>
       </c>
@@ -40818,7 +40866,7 @@
         <v>1191</v>
       </c>
       <c r="L691" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M691" s="2" t="s">
         <v>16</v>
@@ -40842,7 +40890,7 @@
       <c r="T691" s="2"/>
       <c r="U691" s="2"/>
     </row>
-    <row r="692" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>11</v>
       </c>
@@ -40868,7 +40916,7 @@
         <v>13</v>
       </c>
       <c r="L692" s="2" t="s">
-        <v>13</v>
+        <v>1426</v>
       </c>
       <c r="M692" s="2" t="s">
         <v>13</v>
@@ -40892,7 +40940,7 @@
       <c r="T692" s="2"/>
       <c r="U692" s="2"/>
     </row>
-    <row r="693" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>11</v>
       </c>
@@ -40942,7 +40990,7 @@
       <c r="T693" s="2"/>
       <c r="U693" s="2"/>
     </row>
-    <row r="694" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>11</v>
       </c>
@@ -40992,7 +41040,7 @@
       <c r="T694" s="2"/>
       <c r="U694" s="2"/>
     </row>
-    <row r="695" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>11</v>
       </c>
@@ -41042,7 +41090,7 @@
       <c r="T695" s="2"/>
       <c r="U695" s="2"/>
     </row>
-    <row r="696" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>11</v>
       </c>
@@ -41092,7 +41140,7 @@
       <c r="T696" s="2"/>
       <c r="U696" s="2"/>
     </row>
-    <row r="697" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>11</v>
       </c>
@@ -41142,7 +41190,7 @@
       <c r="T697" s="2"/>
       <c r="U697" s="2"/>
     </row>
-    <row r="698" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>11</v>
       </c>
@@ -41366,7 +41414,7 @@
       <c r="T701" s="2"/>
       <c r="U701" s="2"/>
     </row>
-    <row r="702" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>11</v>
       </c>
@@ -41532,7 +41580,7 @@
       <c r="T704" s="2"/>
       <c r="U704" s="2"/>
     </row>
-    <row r="705" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>11</v>
       </c>
@@ -41640,7 +41688,7 @@
       <c r="T706" s="2"/>
       <c r="U706" s="2"/>
     </row>
-    <row r="707" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>11</v>
       </c>
@@ -41690,7 +41738,7 @@
       <c r="T707" s="2"/>
       <c r="U707" s="2"/>
     </row>
-    <row r="708" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>11</v>
       </c>
@@ -41798,7 +41846,7 @@
       <c r="T709" s="2"/>
       <c r="U709" s="2"/>
     </row>
-    <row r="710" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>11</v>
       </c>
@@ -41848,7 +41896,7 @@
       <c r="T710" s="2"/>
       <c r="U710" s="2"/>
     </row>
-    <row r="711" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>11</v>
       </c>
@@ -41956,7 +42004,7 @@
       <c r="T712" s="2"/>
       <c r="U712" s="2"/>
     </row>
-    <row r="713" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>11</v>
       </c>
@@ -42006,7 +42054,7 @@
       <c r="T713" s="2"/>
       <c r="U713" s="2"/>
     </row>
-    <row r="714" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>11</v>
       </c>
@@ -42230,7 +42278,7 @@
       <c r="T717" s="2"/>
       <c r="U717" s="2"/>
     </row>
-    <row r="718" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>11</v>
       </c>
@@ -42280,7 +42328,7 @@
       <c r="T718" s="2"/>
       <c r="U718" s="2"/>
     </row>
-    <row r="719" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:21" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>11</v>
       </c>
@@ -42538,31 +42586,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13"/>
+      <c r="A1" s="17"/>
     </row>
     <row r="2" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
+      <c r="A2" s="17"/>
     </row>
     <row r="3" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
+      <c r="A3" s="17"/>
     </row>
     <row r="4" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
+      <c r="A4" s="17"/>
     </row>
     <row r="5" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
+      <c r="A5" s="17"/>
     </row>
     <row r="6" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
+      <c r="A6" s="17"/>
     </row>
     <row r="7" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13"/>
+      <c r="A7" s="17"/>
     </row>
     <row r="8" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
+      <c r="A8" s="17"/>
     </row>
     <row r="9" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13"/>
+      <c r="A9" s="17"/>
     </row>
     <row r="10" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
@@ -42776,18 +42824,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="18" t="s">
         <v>1421</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="2:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">

--- a/data/upload/packing/TJ-25-26-189.xlsx
+++ b/data/upload/packing/TJ-25-26-189.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\TJ_25-26_189 NE_Gregory LB_SB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\TJ_25-26_189 NE_Gregory LB_SB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD5FF5F-8B84-48AE-95B7-42BAE6401A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D47C6E-02DB-4A40-A1CF-567BB461A204}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spool List" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5918" uniqueCount="1427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5921" uniqueCount="1428">
   <si>
     <t>Project Code</t>
   </si>
@@ -4320,6 +4320,9 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -4393,7 +4396,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4439,6 +4442,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9F9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4537,7 +4546,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4592,6 +4601,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -42870,7 +42882,9 @@
       </c>
     </row>
     <row r="4" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1"/>
+      <c r="B4" s="19" t="s">
+        <v>1427</v>
+      </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
@@ -42890,7 +42904,9 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="1"/>
+      <c r="B5" s="19" t="s">
+        <v>1427</v>
+      </c>
       <c r="C5" s="1">
         <v>2</v>
       </c>
@@ -42910,7 +42926,9 @@
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="2:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="1"/>
+      <c r="B6" s="19" t="s">
+        <v>1427</v>
+      </c>
       <c r="C6" s="1">
         <v>3</v>
       </c>
